--- a/6-descriptive-statistics/starwars.xlsx
+++ b/6-descriptive-statistics/starwars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maryvanvalkenburg/NSS/DDA1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="8_{5B996D39-A8F4-3241-8F2D-45DFE2E5CD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E58E7E8-10A6-4B3D-B167-29F93A856559}"/>
+  <xr:revisionPtr revIDLastSave="563" documentId="8_{5B996D39-A8F4-3241-8F2D-45DFE2E5CD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{436C875B-A585-4194-9014-6FC249236673}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2260" windowWidth="28040" windowHeight="17440" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,25 @@
     <sheet name="starwars" sheetId="1" r:id="rId1"/>
     <sheet name="data_dictionary" sheetId="2" r:id="rId2"/>
     <sheet name="excercises" sheetId="3" r:id="rId3"/>
+    <sheet name="height_filtered" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="chapter1">excercises!$A$1:$A$1</definedName>
     <definedName name="chapter3">excercises!$A$7:$A$7</definedName>
     <definedName name="chapter5">excercises!$A$14:$A$14</definedName>
+    <definedName name="chapter6">excercises!$A$18:$A$18</definedName>
+    <definedName name="character_traits">starwars!$A$2:$T$88</definedName>
+    <definedName name="diff_mean">height_filtered!$X$2:$X$82</definedName>
+    <definedName name="diff_mean_sqd">height_filtered!$Y$2:$Y$82</definedName>
+    <definedName name="filtered_ascending_heights">height_filtered!$U$2:$W$82</definedName>
+    <definedName name="filtered_character_traits">height_filtered!$A$2:$U$82</definedName>
+    <definedName name="filtered_heights">height_filtered!$B$2:$B$82</definedName>
+    <definedName name="height_by_rank">height_filtered!$U$1:$W$82</definedName>
+    <definedName name="height_freq">height_filtered!$V$2:$V$82</definedName>
+    <definedName name="height_order">height_filtered!$U$2:$U$82</definedName>
+    <definedName name="heights">starwars!$B$2:$B$88</definedName>
+    <definedName name="manual_mode_table">height_filtered!$V$2:$W$82</definedName>
+    <definedName name="ordered_height">height_filtered!$W$2:$W$82</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -65,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="333">
   <si>
     <t>name</t>
   </si>
@@ -899,6 +913,9 @@
   </si>
   <si>
     <t>Review the data dictionary. Identify the units of the height and weight columns.</t>
+  </si>
+  <si>
+    <t>=VLOOKUP(DAYS(TODAY(),'excercises'!C13DATE(1995,3,7)),O2:O88,1)</t>
   </si>
   <si>
     <t>Locate Biggs Darklighter’s age. Note the cell address.</t>
@@ -1001,13 +1018,388 @@
   </si>
   <si>
     <t>=FLOOR(CONVERT(E2,"kg","lbm"),0.25)</t>
+  </si>
+  <si>
+    <t>chapter 6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Filter by Character Height:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Filter only characters with height values onto a new sheet.</t>
+    </r>
+  </si>
+  <si>
+    <t>=FILTER(character_traits,ISNUMBER(heights))</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Mean Calculation (without AVERAGE):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Find the mean height using SUM() and COUNT() functions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Median Calculation (without MEDIAN):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Sort the sheet by heigh values in ascending order.
+- Add a new column named height_order to the left of the height column with incrementing numbers.
+- Find the midpoint by dividing the count by 2
+- Use VLOOKUP() to find the midpoint(s) and calculate the median.
+- If there are 2 middlemost values, find the median by calculating the mean of the 2; if there is only 1 middle value, that is the median</t>
+    </r>
+  </si>
+  <si>
+    <t>- =SORT(FILTER(character_traits,ISNUMBER(heights)),COLUMN(heights))</t>
+  </si>
+  <si>
+    <t>=ROW()-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Mode Calculation (without MODE):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Use Conditional Formatting to identify duplicates and find the mode.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Recalculate Mean, Median, and Mode Using Functions:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Use relevant Excel functions to find each value.
+- Compare with manual calculations from earlier steps.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Variance and Standard Deviation Calculation:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Create a diff_mean column, subtracting each height from the mean and copy the formula down the column (remember to use an absolute reference on the mean cell).
+- Create a diff_mean_sqd column by squaring the values in diff_mean.
+- Calculate variance using the average of diff_mean_sqd.
+- Compare with VARP() and STDEVP() function results.</t>
+    </r>
+  </si>
+  <si>
+    <t>=AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</t>
+  </si>
+  <si>
+    <t>=INDEX(diff_mean,ROW()-1)^2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">90th Percentile Calculation:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Calculate the 90th percentile by multiplying COUNT by 0.9 and rounding up.
+- Use VLOOKUP() to find the height for the calculated percentile rank.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Find the First Quartile:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Calculate the 25th percentile manually.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Verify Percentile Using Excel Function:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Use PERCENTILE.INC() to find the 90th percentile and compare with manual results.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Verify Quartile Using Excel Function:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Use QUARTILE.INC() to find the first quartile and compare results with manual calculation.</t>
+    </r>
+  </si>
+  <si>
+    <t>height_order</t>
+  </si>
+  <si>
+    <t>height_freq</t>
+  </si>
+  <si>
+    <t>ordered_height</t>
+  </si>
+  <si>
+    <t>diff_mean</t>
+  </si>
+  <si>
+    <t>diff_mean_sqd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1159,8 +1551,49 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <strike/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <strike/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1346,6 +1779,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1507,7 +1946,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1537,6 +1976,13 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -8007,15 +8453,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C882684-D77A-4A87-900F-85966DA233B8}">
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="50.25" customHeight="1"/>
+  <dimension ref="A1:P28"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="9" style="9"/>
+    <col min="1" max="1" width="7.875" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="70.875" customWidth="1"/>
-    <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.875" customWidth="1"/>
+    <col min="4" max="4" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" ht="50.25" customHeight="1">
+    <row r="1" spans="1:16" s="9" customFormat="1" ht="46.5">
       <c r="A1" s="7" t="s">
         <v>274</v>
       </c>
@@ -8026,7 +8475,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="50.25" customHeight="1">
+    <row r="2" spans="1:16" ht="32.25">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -8036,54 +8485,57 @@
       <c r="C2" s="12" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="50.25" customHeight="1">
+      <c r="P2" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="16.5">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="50.25" customHeight="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="32.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="50.25" customHeight="1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="32.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="50.25" customHeight="1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="32.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="9" customFormat="1" ht="50.25" customHeight="1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="9" customFormat="1" ht="46.5">
       <c r="A7" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>275</v>
@@ -8092,76 +8544,76 @@
         <v>276</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="50.25" customHeight="1">
+    <row r="8" spans="1:16">
       <c r="A8" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="50.25" customHeight="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="32.25">
       <c r="A9" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="50.25" customHeight="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C10" cm="1">
         <f t="array" ref="C10">AVERAGE(_xlfn._xlws.FILTER(starwars!$G2:$G$88,starwars!$G2:$G$88&lt;&gt;0))</f>
         <v>32.048638992833226</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="50.25" customHeight="1">
+    <row r="11" spans="1:16">
       <c r="A11" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="50.25" customHeight="1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="48.75">
       <c r="A12" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="50.25" customHeight="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="16.5">
       <c r="A13" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="9" customFormat="1" ht="50.25" customHeight="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="9" customFormat="1" ht="46.5">
       <c r="A14" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>275</v>
@@ -8170,59 +8622,8579 @@
         <v>276</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="101.25" customHeight="1">
+    <row r="15" spans="1:16" ht="64.5">
       <c r="A15" s="8" t="str" cm="1">
         <f t="array" ref="A15">_xlfn.CONCAT(ROW()-ROW(chapter5),".")</f>
         <v>1.</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="101.25" customHeight="1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="81">
       <c r="A16" s="8" t="str" cm="1">
         <f t="array" ref="A16">_xlfn.CONCAT(ROW()-ROW(chapter5),".")</f>
         <v>2.</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="101.25" customHeight="1">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="81">
       <c r="A17" s="8" t="str" cm="1">
         <f t="array" ref="A17">_xlfn.CONCAT(ROW()-ROW(chapter5),".")</f>
         <v>3.</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="50.25" customHeight="1">
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:3" ht="50.25" customHeight="1">
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:3" ht="50.25" customHeight="1">
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" spans="1:3" ht="50.25" customHeight="1">
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="1:3" ht="50.25" customHeight="1">
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" spans="1:3" ht="50.25" customHeight="1">
-      <c r="B27" s="4"/>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="46.5">
+      <c r="A18" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="48.75">
+      <c r="A19" s="8" t="str" cm="1">
+        <f t="array" ref="A19">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>1.</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="48.75">
+      <c r="A20" s="8" t="str" cm="1">
+        <f t="array" ref="A20">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>2.</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" s="3">
+        <f ca="1">SUM(filtered_heights)/COUNT(filtered_heights)</f>
+        <v>174.35802469135803</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="146.25">
+      <c r="A21" s="8" t="str" cm="1">
+        <f t="array" ref="A21">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>3.</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E21">
+        <f>COUNT(height_order)/2</f>
+        <v>40.5</v>
+      </c>
+      <c r="F21" s="4">
+        <f ca="1">AVERAGE(VLOOKUP(FLOOR(E21,1),filtered_ascending_heights,2),VLOOKUP(CEILING(E21,1),filtered_ascending_heights,2))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="48.75">
+      <c r="A22" s="8" t="str" cm="1">
+        <f t="array" ref="A22">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>4.</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="C22">
+        <f ca="1">VLOOKUP(MAX(height_freq),manual_mode_table,2,FALSE)</f>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="64.5">
+      <c r="A23" s="8" t="str" cm="1">
+        <f t="array" ref="A23">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>5.</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="C23">
+        <f ca="1">AVERAGE(filtered_heights)</f>
+        <v>174.35802469135803</v>
+      </c>
+      <c r="D23">
+        <f ca="1">MEDIAN(filtered_heights)</f>
+        <v>180</v>
+      </c>
+      <c r="E23">
+        <f ca="1">MODE(filtered_heights)</f>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="113.25">
+      <c r="A24" s="8" t="str" cm="1">
+        <f t="array" ref="A24">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>6.</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E24">
+        <f ca="1">AVERAGE(diff_mean_sqd)</f>
+        <v>1194.0570035055634</v>
+      </c>
+      <c r="F24">
+        <f ca="1">VARP(diff_mean)</f>
+        <v>1194.0570035055632</v>
+      </c>
+      <c r="G24">
+        <f ca="1">STDEVP(diff_mean)</f>
+        <v>34.555129915912097</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="64.5">
+      <c r="A25" s="8" t="str" cm="1">
+        <f t="array" ref="A25">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>7.</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="C25">
+        <f ca="1">CEILING(COUNT(ordered_height)*0.9, 1)</f>
+        <v>73</v>
+      </c>
+      <c r="D25">
+        <f ca="1">VLOOKUP(C25,height_by_rank,3)</f>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="48.75">
+      <c r="A26" s="8" t="str" cm="1">
+        <f t="array" ref="A26">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>8.</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="C26">
+        <f ca="1">CEILING(COUNT(ordered_height)*0.25, 1)</f>
+        <v>21</v>
+      </c>
+      <c r="D26">
+        <f ca="1">VLOOKUP(C26,height_by_rank,3)</f>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="48.75">
+      <c r="A27" s="8" t="str" cm="1">
+        <f t="array" ref="A27">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>9.</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="C27">
+        <f ca="1">_xlfn.PERCENTILE.INC(ordered_height,0.9)</f>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="64.5">
+      <c r="A28" s="8" t="str" cm="1">
+        <f t="array" ref="A28">_xlfn.CONCAT(ROW()-ROW(chapter6),".")</f>
+        <v>10.</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="C28">
+        <f ca="1">_xlfn.QUARTILE.INC(ordered_height,1)</f>
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA1D5DBB-C9BB-450E-A8F9-926DDAA5AE1B}">
+  <dimension ref="A1:Y82"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" style="15"/>
+    <col min="22" max="22" width="36" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="32.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="V1" t="s">
+        <v>329</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="X1" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" t="str" cm="1">
+        <f t="array" aca="1" ref="A2:T82" ca="1">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(character_traits,ISNUMBER(heights)),COLUMN(heights))</f>
+        <v>Yoda</v>
+      </c>
+      <c r="B2">
+        <f ca="1"/>
+        <v>66</v>
+      </c>
+      <c r="C2">
+        <f ca="1"/>
+        <v>25.5</v>
+      </c>
+      <c r="D2">
+        <f ca="1"/>
+        <v>0.66</v>
+      </c>
+      <c r="E2">
+        <f ca="1"/>
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <f ca="1"/>
+        <v>37.25</v>
+      </c>
+      <c r="G2">
+        <f ca="1"/>
+        <v>39.026629935720841</v>
+      </c>
+      <c r="H2">
+        <f ca="1"/>
+        <v>5.6965642558855336</v>
+      </c>
+      <c r="I2">
+        <f ca="1"/>
+        <v>3</v>
+      </c>
+      <c r="J2" t="str">
+        <f ca="1"/>
+        <v>white</v>
+      </c>
+      <c r="K2" t="str">
+        <f ca="1"/>
+        <v>green</v>
+      </c>
+      <c r="L2" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M2">
+        <f ca="1"/>
+        <v>896</v>
+      </c>
+      <c r="N2" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <f ca="1"/>
+        <v>327040</v>
+      </c>
+      <c r="P2">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="R2" t="str">
+        <f ca="1"/>
+        <v>Yoda's species</v>
+      </c>
+      <c r="S2" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T2" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith ,  Return of the Jedi ,  The Empire Strikes Back </v>
+      </c>
+      <c r="U2" s="15">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="V2" s="4" cm="1">
+        <f t="array" aca="1" ref="V2" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W2" s="15" cm="1">
+        <f t="array" aca="1" ref="W2:W82" ca="1">filtered_heights</f>
+        <v>66</v>
+      </c>
+      <c r="X2" cm="1">
+        <f t="array" aca="1" ref="X2" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>108.35802469135803</v>
+      </c>
+      <c r="Y2" cm="1">
+        <f t="array" aca="1" ref="Y2" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>11741.461515012956</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" t="str">
+        <f ca="1"/>
+        <v>Ratts Tyerell</v>
+      </c>
+      <c r="B3">
+        <f ca="1"/>
+        <v>79</v>
+      </c>
+      <c r="C3">
+        <f ca="1"/>
+        <v>31</v>
+      </c>
+      <c r="D3">
+        <f ca="1"/>
+        <v>0.79</v>
+      </c>
+      <c r="E3">
+        <f ca="1"/>
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <f ca="1"/>
+        <v>33</v>
+      </c>
+      <c r="G3">
+        <f ca="1"/>
+        <v>24.034609838166958</v>
+      </c>
+      <c r="H3">
+        <f ca="1"/>
+        <v>-9.2954558416683497</v>
+      </c>
+      <c r="I3">
+        <f ca="1"/>
+        <v>32</v>
+      </c>
+      <c r="J3" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K3" t="str">
+        <f ca="1"/>
+        <v>grey, blue</v>
+      </c>
+      <c r="L3" t="str">
+        <f ca="1"/>
+        <v>unknown</v>
+      </c>
+      <c r="M3" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N3" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O3" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P3">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" t="str">
+        <f ca="1"/>
+        <v>Aleen Minor</v>
+      </c>
+      <c r="R3" t="str">
+        <f ca="1"/>
+        <v>Aleena</v>
+      </c>
+      <c r="S3" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T3" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U3" s="15">
+        <f t="shared" ref="U3:U66" si="0">ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="V3" s="4" cm="1">
+        <f t="array" aca="1" ref="V3" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W3" s="15">
+        <f ca="1"/>
+        <v>79</v>
+      </c>
+      <c r="X3" cm="1">
+        <f t="array" aca="1" ref="X3" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>95.358024691358025</v>
+      </c>
+      <c r="Y3" cm="1">
+        <f t="array" aca="1" ref="Y3" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>9093.1528730376467</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" t="str">
+        <f ca="1"/>
+        <v>Wicket Systri Warrick</v>
+      </c>
+      <c r="B4">
+        <f ca="1"/>
+        <v>88</v>
+      </c>
+      <c r="C4">
+        <f ca="1"/>
+        <v>34.5</v>
+      </c>
+      <c r="D4">
+        <f ca="1"/>
+        <v>0.88</v>
+      </c>
+      <c r="E4">
+        <f ca="1"/>
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <f ca="1"/>
+        <v>44</v>
+      </c>
+      <c r="G4">
+        <f ca="1"/>
+        <v>25.826446280991735</v>
+      </c>
+      <c r="H4">
+        <f ca="1"/>
+        <v>-7.503619398843572</v>
+      </c>
+      <c r="I4">
+        <f ca="1"/>
+        <v>21</v>
+      </c>
+      <c r="J4" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K4" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="L4" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M4">
+        <f ca="1"/>
+        <v>8</v>
+      </c>
+      <c r="N4" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <f ca="1"/>
+        <v>2920</v>
+      </c>
+      <c r="P4">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" t="str">
+        <f ca="1"/>
+        <v>Endor</v>
+      </c>
+      <c r="R4" t="str">
+        <f ca="1"/>
+        <v>Ewok</v>
+      </c>
+      <c r="S4" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="T4" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="U4" s="15">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="V4" s="4" cm="1">
+        <f t="array" aca="1" ref="V4" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W4" s="15">
+        <f ca="1"/>
+        <v>88</v>
+      </c>
+      <c r="X4" cm="1">
+        <f t="array" aca="1" ref="X4" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>86.358024691358025</v>
+      </c>
+      <c r="Y4" cm="1">
+        <f t="array" aca="1" ref="Y4" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>7457.7084285932024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" t="str">
+        <f ca="1"/>
+        <v>Dud Bolt</v>
+      </c>
+      <c r="B5">
+        <f ca="1"/>
+        <v>94</v>
+      </c>
+      <c r="C5">
+        <f ca="1"/>
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <f ca="1"/>
+        <v>0.94</v>
+      </c>
+      <c r="E5">
+        <f ca="1"/>
+        <v>45</v>
+      </c>
+      <c r="F5">
+        <f ca="1"/>
+        <v>99</v>
+      </c>
+      <c r="G5">
+        <f ca="1"/>
+        <v>50.928021729289277</v>
+      </c>
+      <c r="H5">
+        <f ca="1"/>
+        <v>17.59795604945397</v>
+      </c>
+      <c r="I5">
+        <f ca="1"/>
+        <v>2</v>
+      </c>
+      <c r="J5" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K5" t="str">
+        <f ca="1"/>
+        <v>blue, grey</v>
+      </c>
+      <c r="L5" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M5" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N5" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O5" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P5">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" t="str">
+        <f ca="1"/>
+        <v>Vulpter</v>
+      </c>
+      <c r="R5" t="str">
+        <f ca="1"/>
+        <v>Vulptereen</v>
+      </c>
+      <c r="S5" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T5" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U5" s="15">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="V5" s="4" cm="1">
+        <f t="array" aca="1" ref="V5" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W5" s="15">
+        <f ca="1"/>
+        <v>94</v>
+      </c>
+      <c r="X5" cm="1">
+        <f t="array" aca="1" ref="X5" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>80.358024691358025</v>
+      </c>
+      <c r="Y5" cm="1">
+        <f t="array" aca="1" ref="Y5" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>6457.4121322969058</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" t="str">
+        <f ca="1"/>
+        <v>R2-D2</v>
+      </c>
+      <c r="B6">
+        <f ca="1"/>
+        <v>96</v>
+      </c>
+      <c r="C6">
+        <f ca="1"/>
+        <v>37.5</v>
+      </c>
+      <c r="D6">
+        <f ca="1"/>
+        <v>0.96</v>
+      </c>
+      <c r="E6">
+        <f ca="1"/>
+        <v>32</v>
+      </c>
+      <c r="F6">
+        <f ca="1"/>
+        <v>70.5</v>
+      </c>
+      <c r="G6">
+        <f ca="1"/>
+        <v>34.722222222222221</v>
+      </c>
+      <c r="H6">
+        <f ca="1"/>
+        <v>1.392156542386914</v>
+      </c>
+      <c r="I6">
+        <f ca="1"/>
+        <v>6</v>
+      </c>
+      <c r="J6" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="K6" t="str">
+        <f ca="1"/>
+        <v>white, blue</v>
+      </c>
+      <c r="L6" t="str">
+        <f ca="1"/>
+        <v>red</v>
+      </c>
+      <c r="M6">
+        <f ca="1"/>
+        <v>33</v>
+      </c>
+      <c r="N6" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <f ca="1"/>
+        <v>12045</v>
+      </c>
+      <c r="P6">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R6" t="str">
+        <f ca="1"/>
+        <v>Droid</v>
+      </c>
+      <c r="S6" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T6" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith ,  Return of the Jedi ,  The Empire Strikes Back ,  A New Hope ,  The Force Awakens </v>
+      </c>
+      <c r="U6" s="15">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="V6" s="4" cm="1">
+        <f t="array" aca="1" ref="V6" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W6" s="15">
+        <f ca="1"/>
+        <v>96</v>
+      </c>
+      <c r="X6" cm="1">
+        <f t="array" aca="1" ref="X6" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>78.358024691358025</v>
+      </c>
+      <c r="Y6" cm="1">
+        <f t="array" aca="1" ref="Y6" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>6139.980033531474</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" t="str">
+        <f ca="1"/>
+        <v>R4-P17</v>
+      </c>
+      <c r="B7">
+        <f ca="1"/>
+        <v>96</v>
+      </c>
+      <c r="C7">
+        <f ca="1"/>
+        <v>37.5</v>
+      </c>
+      <c r="D7">
+        <f ca="1"/>
+        <v>0.96</v>
+      </c>
+      <c r="E7" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F7" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G7">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I7">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J7" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K7" t="str">
+        <f ca="1"/>
+        <v>silver, red</v>
+      </c>
+      <c r="L7" t="str">
+        <f ca="1"/>
+        <v>red, blue</v>
+      </c>
+      <c r="M7" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N7" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O7" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P7">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="R7" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="S7" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T7" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Revenge of the Sith </v>
+      </c>
+      <c r="U7" s="15">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="V7" s="4" cm="1">
+        <f t="array" aca="1" ref="V7" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W7" s="15">
+        <f ca="1"/>
+        <v>96</v>
+      </c>
+      <c r="X7" cm="1">
+        <f t="array" aca="1" ref="X7" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>78.358024691358025</v>
+      </c>
+      <c r="Y7" cm="1">
+        <f t="array" aca="1" ref="Y7" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>6139.980033531474</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" t="str">
+        <f ca="1"/>
+        <v>R5-D4</v>
+      </c>
+      <c r="B8">
+        <f ca="1"/>
+        <v>97</v>
+      </c>
+      <c r="C8">
+        <f ca="1"/>
+        <v>38</v>
+      </c>
+      <c r="D8">
+        <f ca="1"/>
+        <v>0.97</v>
+      </c>
+      <c r="E8">
+        <f ca="1"/>
+        <v>32</v>
+      </c>
+      <c r="F8">
+        <f ca="1"/>
+        <v>70.5</v>
+      </c>
+      <c r="G8">
+        <f ca="1"/>
+        <v>34.009990434690195</v>
+      </c>
+      <c r="H8">
+        <f ca="1"/>
+        <v>0.67992475485488768</v>
+      </c>
+      <c r="I8">
+        <f ca="1"/>
+        <v>8</v>
+      </c>
+      <c r="J8" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="K8" t="str">
+        <f ca="1"/>
+        <v>white, red</v>
+      </c>
+      <c r="L8" t="str">
+        <f ca="1"/>
+        <v>red</v>
+      </c>
+      <c r="M8" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N8" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O8" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P8">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R8" t="str">
+        <f ca="1"/>
+        <v>Droid</v>
+      </c>
+      <c r="S8" t="str">
+        <f ca="1"/>
+        <v>A New Hope</v>
+      </c>
+      <c r="T8" t="str">
+        <f ca="1"/>
+        <v>A New Hope</v>
+      </c>
+      <c r="U8" s="15">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="V8" s="4" cm="1">
+        <f t="array" aca="1" ref="V8" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W8" s="15">
+        <f ca="1"/>
+        <v>97</v>
+      </c>
+      <c r="X8" cm="1">
+        <f t="array" aca="1" ref="X8" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>77.358024691358025</v>
+      </c>
+      <c r="Y8" cm="1">
+        <f t="array" aca="1" ref="Y8" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>5984.263984148758</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" t="str">
+        <f ca="1"/>
+        <v>Sebulba</v>
+      </c>
+      <c r="B9">
+        <f ca="1"/>
+        <v>112</v>
+      </c>
+      <c r="C9">
+        <f ca="1"/>
+        <v>44</v>
+      </c>
+      <c r="D9">
+        <f ca="1"/>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E9">
+        <f ca="1"/>
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <f ca="1"/>
+        <v>88</v>
+      </c>
+      <c r="G9">
+        <f ca="1"/>
+        <v>31.887755102040813</v>
+      </c>
+      <c r="H9">
+        <f ca="1"/>
+        <v>-1.442310577794494</v>
+      </c>
+      <c r="I9">
+        <f ca="1"/>
+        <v>11</v>
+      </c>
+      <c r="J9" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K9" t="str">
+        <f ca="1"/>
+        <v>grey, red</v>
+      </c>
+      <c r="L9" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="M9" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N9" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O9" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P9">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="str">
+        <f ca="1"/>
+        <v>Malastare</v>
+      </c>
+      <c r="R9" t="str">
+        <f ca="1"/>
+        <v>Dug</v>
+      </c>
+      <c r="S9" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T9" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U9" s="15">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="V9" s="4" cm="1">
+        <f t="array" aca="1" ref="V9" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W9" s="15">
+        <f ca="1"/>
+        <v>112</v>
+      </c>
+      <c r="X9" cm="1">
+        <f t="array" aca="1" ref="X9" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>62.358024691358025</v>
+      </c>
+      <c r="Y9" cm="1">
+        <f t="array" aca="1" ref="Y9" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>3888.5232434080172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" t="str">
+        <f ca="1"/>
+        <v>Gasgano</v>
+      </c>
+      <c r="B10">
+        <f ca="1"/>
+        <v>122</v>
+      </c>
+      <c r="C10">
+        <f ca="1"/>
+        <v>48</v>
+      </c>
+      <c r="D10">
+        <f ca="1"/>
+        <v>1.22</v>
+      </c>
+      <c r="E10" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F10" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G10">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I10">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J10" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K10" t="str">
+        <f ca="1"/>
+        <v>white, blue</v>
+      </c>
+      <c r="L10" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="M10" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N10" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O10" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P10">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" t="str">
+        <f ca="1"/>
+        <v>Troiken</v>
+      </c>
+      <c r="R10" t="str">
+        <f ca="1"/>
+        <v>Xexto</v>
+      </c>
+      <c r="S10" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T10" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U10" s="15">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="V10" s="4" cm="1">
+        <f t="array" aca="1" ref="V10" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W10" s="15">
+        <f ca="1"/>
+        <v>122</v>
+      </c>
+      <c r="X10" cm="1">
+        <f t="array" aca="1" ref="X10" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>52.358024691358025</v>
+      </c>
+      <c r="Y10" cm="1">
+        <f t="array" aca="1" ref="Y10" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>2741.3627495808569</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" t="str">
+        <f ca="1"/>
+        <v>Watto</v>
+      </c>
+      <c r="B11">
+        <f ca="1"/>
+        <v>137</v>
+      </c>
+      <c r="C11">
+        <f ca="1"/>
+        <v>53.5</v>
+      </c>
+      <c r="D11">
+        <f ca="1"/>
+        <v>1.37</v>
+      </c>
+      <c r="E11" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F11" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G11">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I11">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J11" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K11" t="str">
+        <f ca="1"/>
+        <v>blue, grey</v>
+      </c>
+      <c r="L11" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M11" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N11" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O11" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P11">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" t="str">
+        <f ca="1"/>
+        <v>Toydaria</v>
+      </c>
+      <c r="R11" t="str">
+        <f ca="1"/>
+        <v>Toydarian</v>
+      </c>
+      <c r="S11" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve"> Attack of the Clones ,  The Phantom Menace </v>
+      </c>
+      <c r="U11" s="15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="V11" s="4" cm="1">
+        <f t="array" aca="1" ref="V11" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W11" s="15">
+        <f ca="1"/>
+        <v>137</v>
+      </c>
+      <c r="X11" cm="1">
+        <f t="array" aca="1" ref="X11" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>37.358024691358025</v>
+      </c>
+      <c r="Y11" cm="1">
+        <f t="array" aca="1" ref="Y11" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>1395.622008840116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" t="str">
+        <f ca="1"/>
+        <v>Leia Organa</v>
+      </c>
+      <c r="B12">
+        <f ca="1"/>
+        <v>150</v>
+      </c>
+      <c r="C12">
+        <f ca="1"/>
+        <v>59</v>
+      </c>
+      <c r="D12">
+        <f ca="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="E12">
+        <f ca="1"/>
+        <v>49</v>
+      </c>
+      <c r="F12">
+        <f ca="1"/>
+        <v>108</v>
+      </c>
+      <c r="G12">
+        <f ca="1"/>
+        <v>21.777777777777779</v>
+      </c>
+      <c r="H12">
+        <f ca="1"/>
+        <v>-11.552287902057529</v>
+      </c>
+      <c r="I12">
+        <f ca="1"/>
+        <v>43</v>
+      </c>
+      <c r="J12" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K12" t="str">
+        <f ca="1"/>
+        <v>light</v>
+      </c>
+      <c r="L12" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M12">
+        <f ca="1"/>
+        <v>19</v>
+      </c>
+      <c r="N12" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <f ca="1"/>
+        <v>6935</v>
+      </c>
+      <c r="P12">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" t="str">
+        <f ca="1"/>
+        <v>Alderaan</v>
+      </c>
+      <c r="R12" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S12" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T12" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Revenge of the Sith ,  Return of the Jedi ,  The Empire Strikes Back ,  A New Hope ,  The Force Awakens </v>
+      </c>
+      <c r="U12" s="15">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="V12" s="4" cm="1">
+        <f t="array" aca="1" ref="V12" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W12" s="15">
+        <f ca="1"/>
+        <v>150</v>
+      </c>
+      <c r="X12" cm="1">
+        <f t="array" aca="1" ref="X12" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>24.358024691358025</v>
+      </c>
+      <c r="Y12" cm="1">
+        <f t="array" aca="1" ref="Y12" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>593.31336686480722</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" t="str">
+        <f ca="1"/>
+        <v>Mon Mothma</v>
+      </c>
+      <c r="B13">
+        <f ca="1"/>
+        <v>150</v>
+      </c>
+      <c r="C13">
+        <f ca="1"/>
+        <v>59</v>
+      </c>
+      <c r="D13">
+        <f ca="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="E13" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F13" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G13">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I13">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J13" t="str">
+        <f ca="1"/>
+        <v>auburn</v>
+      </c>
+      <c r="K13" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L13" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M13">
+        <f ca="1"/>
+        <v>48</v>
+      </c>
+      <c r="N13" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <f ca="1"/>
+        <v>17520</v>
+      </c>
+      <c r="P13">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" t="str">
+        <f ca="1"/>
+        <v>Chandrila</v>
+      </c>
+      <c r="R13" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S13" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="T13" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="U13" s="15">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="V13" s="4" cm="1">
+        <f t="array" aca="1" ref="V13" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W13" s="15">
+        <f ca="1"/>
+        <v>150</v>
+      </c>
+      <c r="X13" cm="1">
+        <f t="array" aca="1" ref="X13" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>24.358024691358025</v>
+      </c>
+      <c r="Y13" cm="1">
+        <f t="array" aca="1" ref="Y13" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>593.31336686480722</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" t="str">
+        <f ca="1"/>
+        <v>Cordé</v>
+      </c>
+      <c r="B14">
+        <f ca="1"/>
+        <v>157</v>
+      </c>
+      <c r="C14">
+        <f ca="1"/>
+        <v>61.5</v>
+      </c>
+      <c r="D14">
+        <f ca="1"/>
+        <v>1.57</v>
+      </c>
+      <c r="E14" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F14" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G14">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I14">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J14" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K14" t="str">
+        <f ca="1"/>
+        <v>light</v>
+      </c>
+      <c r="L14" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M14" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N14" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O14" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P14">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R14" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S14" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T14" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U14" s="15">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="V14" s="4" cm="1">
+        <f t="array" aca="1" ref="V14" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W14" s="15">
+        <f ca="1"/>
+        <v>157</v>
+      </c>
+      <c r="X14" cm="1">
+        <f t="array" aca="1" ref="X14" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>17.358024691358025</v>
+      </c>
+      <c r="Y14" cm="1">
+        <f t="array" aca="1" ref="Y14" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>301.30102118579487</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" t="str">
+        <f ca="1"/>
+        <v>Nien Nunb</v>
+      </c>
+      <c r="B15">
+        <f ca="1"/>
+        <v>160</v>
+      </c>
+      <c r="C15">
+        <f ca="1"/>
+        <v>62.5</v>
+      </c>
+      <c r="D15">
+        <f ca="1"/>
+        <v>1.6</v>
+      </c>
+      <c r="E15">
+        <f ca="1"/>
+        <v>68</v>
+      </c>
+      <c r="F15">
+        <f ca="1"/>
+        <v>149.75</v>
+      </c>
+      <c r="G15">
+        <f ca="1"/>
+        <v>26.562499999999996</v>
+      </c>
+      <c r="H15">
+        <f ca="1"/>
+        <v>-6.767565679835311</v>
+      </c>
+      <c r="I15">
+        <f ca="1"/>
+        <v>16</v>
+      </c>
+      <c r="J15" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K15" t="str">
+        <f ca="1"/>
+        <v>grey</v>
+      </c>
+      <c r="L15" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="M15" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N15" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O15" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P15">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" t="str">
+        <f ca="1"/>
+        <v>Sullust</v>
+      </c>
+      <c r="R15" t="str">
+        <f ca="1"/>
+        <v>Sullustan</v>
+      </c>
+      <c r="S15" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="T15" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="U15" s="15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="V15" s="4" cm="1">
+        <f t="array" aca="1" ref="V15" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W15" s="15">
+        <f ca="1"/>
+        <v>160</v>
+      </c>
+      <c r="X15" cm="1">
+        <f t="array" aca="1" ref="X15" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>14.358024691358025</v>
+      </c>
+      <c r="Y15" cm="1">
+        <f t="array" aca="1" ref="Y15" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>206.15287303764671</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" t="str">
+        <f ca="1"/>
+        <v>Shmi Skywalker</v>
+      </c>
+      <c r="B16">
+        <f ca="1"/>
+        <v>163</v>
+      </c>
+      <c r="C16">
+        <f ca="1"/>
+        <v>64</v>
+      </c>
+      <c r="D16">
+        <f ca="1"/>
+        <v>1.63</v>
+      </c>
+      <c r="E16" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F16" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G16">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I16">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J16" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K16" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L16" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M16">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="N16" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <f ca="1"/>
+        <v>26280</v>
+      </c>
+      <c r="P16">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R16" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S16" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve"> Attack of the Clones ,  The Phantom Menace </v>
+      </c>
+      <c r="U16" s="15">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="V16" s="4" cm="1">
+        <f t="array" aca="1" ref="V16" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W16" s="15">
+        <f ca="1"/>
+        <v>163</v>
+      </c>
+      <c r="X16" cm="1">
+        <f t="array" aca="1" ref="X16" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>11.358024691358025</v>
+      </c>
+      <c r="Y16" cm="1">
+        <f t="array" aca="1" ref="Y16" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>129.00472488949856</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" t="str">
+        <f ca="1"/>
+        <v>Ben Quadinaros</v>
+      </c>
+      <c r="B17">
+        <f ca="1"/>
+        <v>163</v>
+      </c>
+      <c r="C17">
+        <f ca="1"/>
+        <v>64</v>
+      </c>
+      <c r="D17">
+        <f ca="1"/>
+        <v>1.63</v>
+      </c>
+      <c r="E17">
+        <f ca="1"/>
+        <v>65</v>
+      </c>
+      <c r="F17">
+        <f ca="1"/>
+        <v>143.25</v>
+      </c>
+      <c r="G17">
+        <f ca="1"/>
+        <v>24.464601603372351</v>
+      </c>
+      <c r="H17">
+        <f ca="1"/>
+        <v>-8.8654640764629562</v>
+      </c>
+      <c r="I17">
+        <f ca="1"/>
+        <v>31</v>
+      </c>
+      <c r="J17" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K17" t="str">
+        <f ca="1"/>
+        <v>grey, green, yellow</v>
+      </c>
+      <c r="L17" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="M17" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N17" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O17" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P17">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" t="str">
+        <f ca="1"/>
+        <v>Tund</v>
+      </c>
+      <c r="R17" t="str">
+        <f ca="1"/>
+        <v>Toong</v>
+      </c>
+      <c r="S17" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T17" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U17" s="15">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="V17" s="4" cm="1">
+        <f t="array" aca="1" ref="V17" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W17" s="15">
+        <f ca="1"/>
+        <v>163</v>
+      </c>
+      <c r="X17" cm="1">
+        <f t="array" aca="1" ref="X17" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>11.358024691358025</v>
+      </c>
+      <c r="Y17" cm="1">
+        <f t="array" aca="1" ref="Y17" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>129.00472488949856</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" t="str">
+        <f ca="1"/>
+        <v>Beru Whitesun lars</v>
+      </c>
+      <c r="B18">
+        <f ca="1"/>
+        <v>165</v>
+      </c>
+      <c r="C18">
+        <f ca="1"/>
+        <v>64.5</v>
+      </c>
+      <c r="D18">
+        <f ca="1"/>
+        <v>1.65</v>
+      </c>
+      <c r="E18">
+        <f ca="1"/>
+        <v>75</v>
+      </c>
+      <c r="F18">
+        <f ca="1"/>
+        <v>165.25</v>
+      </c>
+      <c r="G18">
+        <f ca="1"/>
+        <v>27.548209366391188</v>
+      </c>
+      <c r="H18">
+        <f ca="1"/>
+        <v>-5.7818563134441199</v>
+      </c>
+      <c r="I18">
+        <f ca="1"/>
+        <v>13</v>
+      </c>
+      <c r="J18" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K18" t="str">
+        <f ca="1"/>
+        <v>light</v>
+      </c>
+      <c r="L18" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M18">
+        <f ca="1"/>
+        <v>47</v>
+      </c>
+      <c r="N18" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <f ca="1"/>
+        <v>17155</v>
+      </c>
+      <c r="P18">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R18" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S18" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T18" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Revenge of the Sith ,  A New Hope </v>
+      </c>
+      <c r="U18" s="15">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="V18" s="4" cm="1">
+        <f t="array" aca="1" ref="V18" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W18" s="15">
+        <f ca="1"/>
+        <v>165</v>
+      </c>
+      <c r="X18" cm="1">
+        <f t="array" aca="1" ref="X18" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>9.3580246913580254</v>
+      </c>
+      <c r="Y18" cm="1">
+        <f t="array" aca="1" ref="Y18" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>87.57262612406646</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" t="str">
+        <f ca="1"/>
+        <v>Dormé</v>
+      </c>
+      <c r="B19">
+        <f ca="1"/>
+        <v>165</v>
+      </c>
+      <c r="C19">
+        <f ca="1"/>
+        <v>64.5</v>
+      </c>
+      <c r="D19">
+        <f ca="1"/>
+        <v>1.65</v>
+      </c>
+      <c r="E19" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F19" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G19">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I19">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J19" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K19" t="str">
+        <f ca="1"/>
+        <v>light</v>
+      </c>
+      <c r="L19" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M19" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N19" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O19" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P19">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R19" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S19" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T19" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U19" s="15">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="V19" s="4" cm="1">
+        <f t="array" aca="1" ref="V19" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W19" s="15">
+        <f ca="1"/>
+        <v>165</v>
+      </c>
+      <c r="X19" cm="1">
+        <f t="array" aca="1" ref="X19" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>9.3580246913580254</v>
+      </c>
+      <c r="Y19" cm="1">
+        <f t="array" aca="1" ref="Y19" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>87.57262612406646</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" t="str">
+        <f ca="1"/>
+        <v>Padmé Amidala</v>
+      </c>
+      <c r="B20">
+        <f ca="1"/>
+        <v>165</v>
+      </c>
+      <c r="C20">
+        <f ca="1"/>
+        <v>64.5</v>
+      </c>
+      <c r="D20">
+        <f ca="1"/>
+        <v>1.65</v>
+      </c>
+      <c r="E20">
+        <f ca="1"/>
+        <v>45</v>
+      </c>
+      <c r="F20">
+        <f ca="1"/>
+        <v>99</v>
+      </c>
+      <c r="G20">
+        <f ca="1"/>
+        <v>16.528925619834713</v>
+      </c>
+      <c r="H20">
+        <f ca="1"/>
+        <v>-16.801140060000595</v>
+      </c>
+      <c r="I20">
+        <f ca="1"/>
+        <v>55</v>
+      </c>
+      <c r="J20" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K20" t="str">
+        <f ca="1"/>
+        <v>light</v>
+      </c>
+      <c r="L20" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M20">
+        <f ca="1"/>
+        <v>46</v>
+      </c>
+      <c r="N20" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <f ca="1"/>
+        <v>16790</v>
+      </c>
+      <c r="P20">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R20" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S20" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T20" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U20" s="15">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V20" s="4" cm="1">
+        <f t="array" aca="1" ref="V20" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W20" s="15">
+        <f ca="1"/>
+        <v>165</v>
+      </c>
+      <c r="X20" cm="1">
+        <f t="array" aca="1" ref="X20" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>9.3580246913580254</v>
+      </c>
+      <c r="Y20" cm="1">
+        <f t="array" aca="1" ref="Y20" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>87.57262612406646</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" t="str">
+        <f ca="1"/>
+        <v>Barriss Offee</v>
+      </c>
+      <c r="B21">
+        <f ca="1"/>
+        <v>166</v>
+      </c>
+      <c r="C21">
+        <f ca="1"/>
+        <v>65</v>
+      </c>
+      <c r="D21">
+        <f ca="1"/>
+        <v>1.66</v>
+      </c>
+      <c r="E21">
+        <f ca="1"/>
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <f ca="1"/>
+        <v>110</v>
+      </c>
+      <c r="G21">
+        <f ca="1"/>
+        <v>18.144868631151112</v>
+      </c>
+      <c r="H21">
+        <f ca="1"/>
+        <v>-15.185197048684195</v>
+      </c>
+      <c r="I21">
+        <f ca="1"/>
+        <v>50</v>
+      </c>
+      <c r="J21" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K21" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="L21" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M21">
+        <f ca="1"/>
+        <v>40</v>
+      </c>
+      <c r="N21" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <f ca="1"/>
+        <v>14600</v>
+      </c>
+      <c r="P21">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" t="str">
+        <f ca="1"/>
+        <v>Mirial</v>
+      </c>
+      <c r="R21" t="str">
+        <f ca="1"/>
+        <v>Mirialan</v>
+      </c>
+      <c r="S21" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T21" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U21" s="15">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="V21" s="4" cm="1">
+        <f t="array" aca="1" ref="V21" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W21" s="15">
+        <f ca="1"/>
+        <v>166</v>
+      </c>
+      <c r="X21" cm="1">
+        <f t="array" aca="1" ref="X21" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>8.3580246913580254</v>
+      </c>
+      <c r="Y21" cm="1">
+        <f t="array" aca="1" ref="Y21" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>69.856576741350409</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" t="str">
+        <f ca="1"/>
+        <v>C-3PO</v>
+      </c>
+      <c r="B22">
+        <f ca="1"/>
+        <v>167</v>
+      </c>
+      <c r="C22">
+        <f ca="1"/>
+        <v>65.5</v>
+      </c>
+      <c r="D22">
+        <f ca="1"/>
+        <v>1.67</v>
+      </c>
+      <c r="E22">
+        <f ca="1"/>
+        <v>75</v>
+      </c>
+      <c r="F22">
+        <f ca="1"/>
+        <v>165.25</v>
+      </c>
+      <c r="G22">
+        <f ca="1"/>
+        <v>26.892323138154829</v>
+      </c>
+      <c r="H22">
+        <f ca="1"/>
+        <v>-6.4377425416804783</v>
+      </c>
+      <c r="I22">
+        <f ca="1"/>
+        <v>14</v>
+      </c>
+      <c r="J22" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="K22" t="str">
+        <f ca="1"/>
+        <v>gold</v>
+      </c>
+      <c r="L22" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M22">
+        <f ca="1"/>
+        <v>112</v>
+      </c>
+      <c r="N22" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <f ca="1"/>
+        <v>40880</v>
+      </c>
+      <c r="P22">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R22" t="str">
+        <f ca="1"/>
+        <v>Droid</v>
+      </c>
+      <c r="S22" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T22" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith ,  Return of the Jedi ,  The Empire Strikes Back ,  A New Hope </v>
+      </c>
+      <c r="U22" s="15">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="V22" s="4" cm="1">
+        <f t="array" aca="1" ref="V22" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W22" s="15">
+        <f ca="1"/>
+        <v>167</v>
+      </c>
+      <c r="X22" cm="1">
+        <f t="array" aca="1" ref="X22" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>7.3580246913580254</v>
+      </c>
+      <c r="Y22" cm="1">
+        <f t="array" aca="1" ref="Y22" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>54.140527358634365</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" t="str">
+        <f ca="1"/>
+        <v>Jocasta Nu</v>
+      </c>
+      <c r="B23">
+        <f ca="1"/>
+        <v>167</v>
+      </c>
+      <c r="C23">
+        <f ca="1"/>
+        <v>65.5</v>
+      </c>
+      <c r="D23">
+        <f ca="1"/>
+        <v>1.67</v>
+      </c>
+      <c r="E23" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F23" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G23">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I23">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J23" t="str">
+        <f ca="1"/>
+        <v>white</v>
+      </c>
+      <c r="K23" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L23" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M23" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N23" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O23" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P23">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" t="str">
+        <f ca="1"/>
+        <v>Coruscant</v>
+      </c>
+      <c r="R23" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S23" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T23" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U23" s="15">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="V23" s="4" cm="1">
+        <f t="array" aca="1" ref="V23" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W23" s="15">
+        <f ca="1"/>
+        <v>167</v>
+      </c>
+      <c r="X23" cm="1">
+        <f t="array" aca="1" ref="X23" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>7.3580246913580254</v>
+      </c>
+      <c r="Y23" cm="1">
+        <f t="array" aca="1" ref="Y23" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>54.140527358634365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" t="str">
+        <f ca="1"/>
+        <v>Zam Wesell</v>
+      </c>
+      <c r="B24">
+        <f ca="1"/>
+        <v>168</v>
+      </c>
+      <c r="C24">
+        <f ca="1"/>
+        <v>66</v>
+      </c>
+      <c r="D24">
+        <f ca="1"/>
+        <v>1.68</v>
+      </c>
+      <c r="E24">
+        <f ca="1"/>
+        <v>55</v>
+      </c>
+      <c r="F24">
+        <f ca="1"/>
+        <v>121.25</v>
+      </c>
+      <c r="G24">
+        <f ca="1"/>
+        <v>19.486961451247168</v>
+      </c>
+      <c r="H24">
+        <f ca="1"/>
+        <v>-13.843104228588139</v>
+      </c>
+      <c r="I24">
+        <f ca="1"/>
+        <v>47</v>
+      </c>
+      <c r="J24" t="str">
+        <f ca="1"/>
+        <v>blonde</v>
+      </c>
+      <c r="K24" t="str">
+        <f ca="1"/>
+        <v>fair, green, yellow</v>
+      </c>
+      <c r="L24" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M24" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N24" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O24" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P24">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" t="str">
+        <f ca="1"/>
+        <v>Zolan</v>
+      </c>
+      <c r="R24" t="str">
+        <f ca="1"/>
+        <v>Clawdite</v>
+      </c>
+      <c r="S24" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T24" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U24" s="15">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="V24" s="4" cm="1">
+        <f t="array" aca="1" ref="V24" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W24" s="15">
+        <f ca="1"/>
+        <v>168</v>
+      </c>
+      <c r="X24" cm="1">
+        <f t="array" aca="1" ref="X24" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>6.3580246913580254</v>
+      </c>
+      <c r="Y24" cm="1">
+        <f t="array" aca="1" ref="Y24" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>40.424477975918315</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" t="str">
+        <f ca="1"/>
+        <v>Wedge Antilles</v>
+      </c>
+      <c r="B25">
+        <f ca="1"/>
+        <v>170</v>
+      </c>
+      <c r="C25">
+        <f ca="1"/>
+        <v>66.5</v>
+      </c>
+      <c r="D25">
+        <f ca="1"/>
+        <v>1.7</v>
+      </c>
+      <c r="E25">
+        <f ca="1"/>
+        <v>77</v>
+      </c>
+      <c r="F25">
+        <f ca="1"/>
+        <v>169.75</v>
+      </c>
+      <c r="G25">
+        <f ca="1"/>
+        <v>26.643598615916957</v>
+      </c>
+      <c r="H25">
+        <f ca="1"/>
+        <v>-6.6864670639183501</v>
+      </c>
+      <c r="I25">
+        <f ca="1"/>
+        <v>15</v>
+      </c>
+      <c r="J25" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K25" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L25" t="str">
+        <f ca="1"/>
+        <v>hazel</v>
+      </c>
+      <c r="M25">
+        <f ca="1"/>
+        <v>21</v>
+      </c>
+      <c r="N25" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <f ca="1"/>
+        <v>7665</v>
+      </c>
+      <c r="P25">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" t="str">
+        <f ca="1"/>
+        <v>Corellia</v>
+      </c>
+      <c r="R25" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S25" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="T25" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Return of the Jedi ,  The Empire Strikes Back ,  A New Hope </v>
+      </c>
+      <c r="U25" s="15">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="V25" s="4" cm="1">
+        <f t="array" aca="1" ref="V25" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>4</v>
+      </c>
+      <c r="W25" s="15">
+        <f ca="1"/>
+        <v>170</v>
+      </c>
+      <c r="X25" cm="1">
+        <f t="array" aca="1" ref="X25" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>4.3580246913580254</v>
+      </c>
+      <c r="Y25" cm="1">
+        <f t="array" aca="1" ref="Y25" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>18.992379210486213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" t="str">
+        <f ca="1"/>
+        <v>Palpatine</v>
+      </c>
+      <c r="B26">
+        <f ca="1"/>
+        <v>170</v>
+      </c>
+      <c r="C26">
+        <f ca="1"/>
+        <v>66.5</v>
+      </c>
+      <c r="D26">
+        <f ca="1"/>
+        <v>1.7</v>
+      </c>
+      <c r="E26">
+        <f ca="1"/>
+        <v>75</v>
+      </c>
+      <c r="F26">
+        <f ca="1"/>
+        <v>165.25</v>
+      </c>
+      <c r="G26">
+        <f ca="1"/>
+        <v>25.95155709342561</v>
+      </c>
+      <c r="H26">
+        <f ca="1"/>
+        <v>-7.3785085864096978</v>
+      </c>
+      <c r="I26">
+        <f ca="1"/>
+        <v>20</v>
+      </c>
+      <c r="J26" t="str">
+        <f ca="1"/>
+        <v>grey</v>
+      </c>
+      <c r="K26" t="str">
+        <f ca="1"/>
+        <v>pale</v>
+      </c>
+      <c r="L26" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M26">
+        <f ca="1"/>
+        <v>82</v>
+      </c>
+      <c r="N26" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <f ca="1"/>
+        <v>29930</v>
+      </c>
+      <c r="P26">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R26" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S26" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve"> Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith ,  Return of the Jedi ,  The Empire Strikes Back </v>
+      </c>
+      <c r="U26" s="15">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="V26" s="4" cm="1">
+        <f t="array" aca="1" ref="V26" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>4</v>
+      </c>
+      <c r="W26" s="15">
+        <f ca="1"/>
+        <v>170</v>
+      </c>
+      <c r="X26" cm="1">
+        <f t="array" aca="1" ref="X26" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>4.3580246913580254</v>
+      </c>
+      <c r="Y26" cm="1">
+        <f t="array" aca="1" ref="Y26" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>18.992379210486213</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" t="str">
+        <f ca="1"/>
+        <v>Finis Valorum</v>
+      </c>
+      <c r="B27">
+        <f ca="1"/>
+        <v>170</v>
+      </c>
+      <c r="C27">
+        <f ca="1"/>
+        <v>66.5</v>
+      </c>
+      <c r="D27">
+        <f ca="1"/>
+        <v>1.7</v>
+      </c>
+      <c r="E27" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F27" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G27">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I27">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J27" t="str">
+        <f ca="1"/>
+        <v>blond</v>
+      </c>
+      <c r="K27" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L27" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M27">
+        <f ca="1"/>
+        <v>91</v>
+      </c>
+      <c r="N27" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <f ca="1"/>
+        <v>33215</v>
+      </c>
+      <c r="P27">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" t="str">
+        <f ca="1"/>
+        <v>Coruscant</v>
+      </c>
+      <c r="R27" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S27" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T27" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U27" s="15">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="V27" s="4" cm="1">
+        <f t="array" aca="1" ref="V27" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>4</v>
+      </c>
+      <c r="W27" s="15">
+        <f ca="1"/>
+        <v>170</v>
+      </c>
+      <c r="X27" cm="1">
+        <f t="array" aca="1" ref="X27" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>4.3580246913580254</v>
+      </c>
+      <c r="Y27" cm="1">
+        <f t="array" aca="1" ref="Y27" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>18.992379210486213</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" t="str">
+        <f ca="1"/>
+        <v>Luminara Unduli</v>
+      </c>
+      <c r="B28">
+        <f ca="1"/>
+        <v>170</v>
+      </c>
+      <c r="C28">
+        <f ca="1"/>
+        <v>66.5</v>
+      </c>
+      <c r="D28">
+        <f ca="1"/>
+        <v>1.7</v>
+      </c>
+      <c r="E28">
+        <f ca="1"/>
+        <v>56.2</v>
+      </c>
+      <c r="F28">
+        <f ca="1"/>
+        <v>123.75</v>
+      </c>
+      <c r="G28">
+        <f ca="1"/>
+        <v>19.446366782006923</v>
+      </c>
+      <c r="H28">
+        <f ca="1"/>
+        <v>-13.883698897828385</v>
+      </c>
+      <c r="I28">
+        <f ca="1"/>
+        <v>48</v>
+      </c>
+      <c r="J28" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K28" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="L28" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M28">
+        <f ca="1"/>
+        <v>58</v>
+      </c>
+      <c r="N28" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <f ca="1"/>
+        <v>21170</v>
+      </c>
+      <c r="P28">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" t="str">
+        <f ca="1"/>
+        <v>Mirial</v>
+      </c>
+      <c r="R28" t="str">
+        <f ca="1"/>
+        <v>Mirialan</v>
+      </c>
+      <c r="S28" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T28" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Revenge of the Sith </v>
+      </c>
+      <c r="U28" s="15">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="V28" s="4" cm="1">
+        <f t="array" aca="1" ref="V28" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>4</v>
+      </c>
+      <c r="W28" s="15">
+        <f ca="1"/>
+        <v>170</v>
+      </c>
+      <c r="X28" cm="1">
+        <f t="array" aca="1" ref="X28" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>4.3580246913580254</v>
+      </c>
+      <c r="Y28" cm="1">
+        <f t="array" aca="1" ref="Y28" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>18.992379210486213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" t="str">
+        <f ca="1"/>
+        <v>Eeth Koth</v>
+      </c>
+      <c r="B29">
+        <f ca="1"/>
+        <v>171</v>
+      </c>
+      <c r="C29">
+        <f ca="1"/>
+        <v>67</v>
+      </c>
+      <c r="D29">
+        <f ca="1"/>
+        <v>1.71</v>
+      </c>
+      <c r="E29" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F29" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G29">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I29">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J29" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K29" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="L29" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M29" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N29" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O29" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P29">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" t="str">
+        <f ca="1"/>
+        <v>Iridonia</v>
+      </c>
+      <c r="R29" t="str">
+        <f ca="1"/>
+        <v>Zabrak</v>
+      </c>
+      <c r="S29" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T29" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U29" s="15">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="V29" s="4" cm="1">
+        <f t="array" aca="1" ref="V29" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W29" s="15">
+        <f ca="1"/>
+        <v>171</v>
+      </c>
+      <c r="X29" cm="1">
+        <f t="array" aca="1" ref="X29" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>3.3580246913580254</v>
+      </c>
+      <c r="Y29" cm="1">
+        <f t="array" aca="1" ref="Y29" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>11.276329827770162</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" t="str">
+        <f ca="1"/>
+        <v>Luke Skywalker</v>
+      </c>
+      <c r="B30">
+        <f ca="1"/>
+        <v>172</v>
+      </c>
+      <c r="C30">
+        <f ca="1"/>
+        <v>67.5</v>
+      </c>
+      <c r="D30">
+        <f ca="1"/>
+        <v>1.72</v>
+      </c>
+      <c r="E30">
+        <f ca="1"/>
+        <v>77</v>
+      </c>
+      <c r="F30">
+        <f ca="1"/>
+        <v>169.75</v>
+      </c>
+      <c r="G30">
+        <f ca="1"/>
+        <v>26.027582477014604</v>
+      </c>
+      <c r="H30">
+        <f ca="1"/>
+        <v>-7.302483202820703</v>
+      </c>
+      <c r="I30">
+        <f ca="1"/>
+        <v>18</v>
+      </c>
+      <c r="J30" t="str">
+        <f ca="1"/>
+        <v>blond</v>
+      </c>
+      <c r="K30" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L30" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M30">
+        <f ca="1"/>
+        <v>19</v>
+      </c>
+      <c r="N30" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <f ca="1"/>
+        <v>6935</v>
+      </c>
+      <c r="P30">
+        <f ca="1"/>
+        <v>5475</v>
+      </c>
+      <c r="Q30" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R30" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S30" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T30" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Revenge of the Sith ,  Return of the Jedi ,  The Empire Strikes Back ,  A New Hope ,  The Force Awakens  </v>
+      </c>
+      <c r="U30" s="15">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="V30" s="4" cm="1">
+        <f t="array" aca="1" ref="V30" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W30" s="15">
+        <f ca="1"/>
+        <v>172</v>
+      </c>
+      <c r="X30" cm="1">
+        <f t="array" aca="1" ref="X30" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>2.3580246913580254</v>
+      </c>
+      <c r="Y30" cm="1">
+        <f t="array" aca="1" ref="Y30" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>5.5602804450541106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" t="str">
+        <f ca="1"/>
+        <v>Greedo</v>
+      </c>
+      <c r="B31">
+        <f ca="1"/>
+        <v>173</v>
+      </c>
+      <c r="C31">
+        <f ca="1"/>
+        <v>68</v>
+      </c>
+      <c r="D31">
+        <f ca="1"/>
+        <v>1.73</v>
+      </c>
+      <c r="E31">
+        <f ca="1"/>
+        <v>74</v>
+      </c>
+      <c r="F31">
+        <f ca="1"/>
+        <v>163</v>
+      </c>
+      <c r="G31">
+        <f ca="1"/>
+        <v>24.725182932941294</v>
+      </c>
+      <c r="H31">
+        <f ca="1"/>
+        <v>-8.6048827468940132</v>
+      </c>
+      <c r="I31">
+        <f ca="1"/>
+        <v>28</v>
+      </c>
+      <c r="J31" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="K31" t="str">
+        <f ca="1"/>
+        <v>green</v>
+      </c>
+      <c r="L31" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="M31">
+        <f ca="1"/>
+        <v>44</v>
+      </c>
+      <c r="N31" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <f ca="1"/>
+        <v>16060</v>
+      </c>
+      <c r="P31">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="str">
+        <f ca="1"/>
+        <v>Rodia</v>
+      </c>
+      <c r="R31" t="str">
+        <f ca="1"/>
+        <v>Rodian</v>
+      </c>
+      <c r="S31" t="str">
+        <f ca="1"/>
+        <v>A New Hope</v>
+      </c>
+      <c r="T31" t="str">
+        <f ca="1"/>
+        <v>A New Hope</v>
+      </c>
+      <c r="U31" s="15">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="V31" s="4" cm="1">
+        <f t="array" aca="1" ref="V31" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W31" s="15">
+        <f ca="1"/>
+        <v>173</v>
+      </c>
+      <c r="X31" cm="1">
+        <f t="array" aca="1" ref="X31" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>1.3580246913580254</v>
+      </c>
+      <c r="Y31" cm="1">
+        <f t="array" aca="1" ref="Y31" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>1.8442310623380602</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="A32" t="str">
+        <f ca="1"/>
+        <v>Jabba Desilijic Tiure</v>
+      </c>
+      <c r="B32">
+        <f ca="1"/>
+        <v>175</v>
+      </c>
+      <c r="C32">
+        <f ca="1"/>
+        <v>68.5</v>
+      </c>
+      <c r="D32">
+        <f ca="1"/>
+        <v>1.75</v>
+      </c>
+      <c r="E32">
+        <f ca="1"/>
+        <v>1358</v>
+      </c>
+      <c r="F32">
+        <f ca="1"/>
+        <v>2993.75</v>
+      </c>
+      <c r="G32">
+        <f ca="1"/>
+        <v>443.42857142857144</v>
+      </c>
+      <c r="H32">
+        <f ca="1"/>
+        <v>410.09850574873616</v>
+      </c>
+      <c r="I32">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="J32" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="K32" t="str">
+        <f ca="1"/>
+        <v>green-tan, brown</v>
+      </c>
+      <c r="L32" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="M32">
+        <f ca="1"/>
+        <v>600</v>
+      </c>
+      <c r="N32" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O32">
+        <f ca="1"/>
+        <v>219000</v>
+      </c>
+      <c r="P32">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" t="str">
+        <f ca="1"/>
+        <v>Nal Hutta</v>
+      </c>
+      <c r="R32" t="str">
+        <f ca="1"/>
+        <v>Hutt</v>
+      </c>
+      <c r="S32" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T32" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">The Phantom Menace ,  Return of the Jedi ,  A New Hope </v>
+      </c>
+      <c r="U32" s="15">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="V32" s="4" cm="1">
+        <f t="array" aca="1" ref="V32" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W32" s="15">
+        <f ca="1"/>
+        <v>175</v>
+      </c>
+      <c r="X32" cm="1">
+        <f t="array" aca="1" ref="X32" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-0.64197530864197461</v>
+      </c>
+      <c r="Y32" cm="1">
+        <f t="array" aca="1" ref="Y32" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>0.41213229690595854</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
+      <c r="A33" t="str">
+        <f ca="1"/>
+        <v>Lobot</v>
+      </c>
+      <c r="B33">
+        <f ca="1"/>
+        <v>175</v>
+      </c>
+      <c r="C33">
+        <f ca="1"/>
+        <v>68.5</v>
+      </c>
+      <c r="D33">
+        <f ca="1"/>
+        <v>1.75</v>
+      </c>
+      <c r="E33">
+        <f ca="1"/>
+        <v>79</v>
+      </c>
+      <c r="F33">
+        <f ca="1"/>
+        <v>174</v>
+      </c>
+      <c r="G33">
+        <f ca="1"/>
+        <v>25.795918367346939</v>
+      </c>
+      <c r="H33">
+        <f ca="1"/>
+        <v>-7.5341473124883684</v>
+      </c>
+      <c r="I33">
+        <f ca="1"/>
+        <v>22</v>
+      </c>
+      <c r="J33" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K33" t="str">
+        <f ca="1"/>
+        <v>light</v>
+      </c>
+      <c r="L33" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M33">
+        <f ca="1"/>
+        <v>37</v>
+      </c>
+      <c r="N33" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <f ca="1"/>
+        <v>13505</v>
+      </c>
+      <c r="P33">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q33" t="str">
+        <f ca="1"/>
+        <v>Bespin</v>
+      </c>
+      <c r="R33" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S33" t="str">
+        <f ca="1"/>
+        <v>The Empire Strikes Back</v>
+      </c>
+      <c r="T33" t="str">
+        <f ca="1"/>
+        <v>The Empire Strikes Back</v>
+      </c>
+      <c r="U33" s="15">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="V33" s="4" cm="1">
+        <f t="array" aca="1" ref="V33" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W33" s="15">
+        <f ca="1"/>
+        <v>175</v>
+      </c>
+      <c r="X33" cm="1">
+        <f t="array" aca="1" ref="X33" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-0.64197530864197461</v>
+      </c>
+      <c r="Y33" cm="1">
+        <f t="array" aca="1" ref="Y33" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>0.41213229690595854</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
+      <c r="A34" t="str">
+        <f ca="1"/>
+        <v>Darth Maul</v>
+      </c>
+      <c r="B34">
+        <f ca="1"/>
+        <v>175</v>
+      </c>
+      <c r="C34">
+        <f ca="1"/>
+        <v>68.5</v>
+      </c>
+      <c r="D34">
+        <f ca="1"/>
+        <v>1.75</v>
+      </c>
+      <c r="E34">
+        <f ca="1"/>
+        <v>80</v>
+      </c>
+      <c r="F34">
+        <f ca="1"/>
+        <v>176.25</v>
+      </c>
+      <c r="G34">
+        <f ca="1"/>
+        <v>26.122448979591837</v>
+      </c>
+      <c r="H34">
+        <f ca="1"/>
+        <v>-7.2076167002434701</v>
+      </c>
+      <c r="I34">
+        <f ca="1"/>
+        <v>17</v>
+      </c>
+      <c r="J34" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K34" t="str">
+        <f ca="1"/>
+        <v>red</v>
+      </c>
+      <c r="L34" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M34">
+        <f ca="1"/>
+        <v>54</v>
+      </c>
+      <c r="N34" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <f ca="1"/>
+        <v>19710</v>
+      </c>
+      <c r="P34">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="str">
+        <f ca="1"/>
+        <v>Dathomir</v>
+      </c>
+      <c r="R34" t="str">
+        <f ca="1"/>
+        <v>Zabrak</v>
+      </c>
+      <c r="S34" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T34" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U34" s="15">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="V34" s="4" cm="1">
+        <f t="array" aca="1" ref="V34" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W34" s="15">
+        <f ca="1"/>
+        <v>175</v>
+      </c>
+      <c r="X34" cm="1">
+        <f t="array" aca="1" ref="X34" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-0.64197530864197461</v>
+      </c>
+      <c r="Y34" cm="1">
+        <f t="array" aca="1" ref="Y34" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>0.41213229690595854</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" t="str">
+        <f ca="1"/>
+        <v>Lando Calrissian</v>
+      </c>
+      <c r="B35">
+        <f ca="1"/>
+        <v>177</v>
+      </c>
+      <c r="C35">
+        <f ca="1"/>
+        <v>69.5</v>
+      </c>
+      <c r="D35">
+        <f ca="1"/>
+        <v>1.77</v>
+      </c>
+      <c r="E35">
+        <f ca="1"/>
+        <v>79</v>
+      </c>
+      <c r="F35">
+        <f ca="1"/>
+        <v>174</v>
+      </c>
+      <c r="G35">
+        <f ca="1"/>
+        <v>25.216253311628201</v>
+      </c>
+      <c r="H35">
+        <f ca="1"/>
+        <v>-8.1138123682071068</v>
+      </c>
+      <c r="I35">
+        <f ca="1"/>
+        <v>24</v>
+      </c>
+      <c r="J35" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K35" t="str">
+        <f ca="1"/>
+        <v>dark</v>
+      </c>
+      <c r="L35" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M35">
+        <f ca="1"/>
+        <v>31</v>
+      </c>
+      <c r="N35" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <f ca="1"/>
+        <v>11315</v>
+      </c>
+      <c r="P35">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" t="str">
+        <f ca="1"/>
+        <v>Socorro</v>
+      </c>
+      <c r="R35" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S35" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="T35" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Return of the Jedi ,  The Empire Strikes Back </v>
+      </c>
+      <c r="U35" s="15">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="V35" s="4" cm="1">
+        <f t="array" aca="1" ref="V35" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W35" s="15">
+        <f ca="1"/>
+        <v>177</v>
+      </c>
+      <c r="X35" cm="1">
+        <f t="array" aca="1" ref="X35" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-2.6419753086419746</v>
+      </c>
+      <c r="Y35" cm="1">
+        <f t="array" aca="1" ref="Y35" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>6.9800335314738566</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
+      <c r="A36" t="str">
+        <f ca="1"/>
+        <v>Owen Lars</v>
+      </c>
+      <c r="B36">
+        <f ca="1"/>
+        <v>178</v>
+      </c>
+      <c r="C36">
+        <f ca="1"/>
+        <v>70</v>
+      </c>
+      <c r="D36">
+        <f ca="1"/>
+        <v>1.78</v>
+      </c>
+      <c r="E36">
+        <f ca="1"/>
+        <v>120</v>
+      </c>
+      <c r="F36">
+        <f ca="1"/>
+        <v>264.5</v>
+      </c>
+      <c r="G36">
+        <f ca="1"/>
+        <v>37.874005807347558</v>
+      </c>
+      <c r="H36">
+        <f ca="1"/>
+        <v>4.5439401275122506</v>
+      </c>
+      <c r="I36">
+        <f ca="1"/>
+        <v>4</v>
+      </c>
+      <c r="J36" t="str">
+        <f ca="1"/>
+        <v>brown, grey</v>
+      </c>
+      <c r="K36" t="str">
+        <f ca="1"/>
+        <v>light</v>
+      </c>
+      <c r="L36" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M36">
+        <f ca="1"/>
+        <v>52</v>
+      </c>
+      <c r="N36" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <f ca="1"/>
+        <v>18980</v>
+      </c>
+      <c r="P36">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R36" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S36" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T36" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Revenge of the Sith ,  A New Hope </v>
+      </c>
+      <c r="U36" s="15">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="V36" s="4" cm="1">
+        <f t="array" aca="1" ref="V36" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>4</v>
+      </c>
+      <c r="W36" s="15">
+        <f ca="1"/>
+        <v>178</v>
+      </c>
+      <c r="X36" cm="1">
+        <f t="array" aca="1" ref="X36" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-3.6419753086419746</v>
+      </c>
+      <c r="Y36" cm="1">
+        <f t="array" aca="1" ref="Y36" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>13.263984148757807</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
+      <c r="A37" t="str">
+        <f ca="1"/>
+        <v>Ayla Secura</v>
+      </c>
+      <c r="B37">
+        <f ca="1"/>
+        <v>178</v>
+      </c>
+      <c r="C37">
+        <f ca="1"/>
+        <v>70</v>
+      </c>
+      <c r="D37">
+        <f ca="1"/>
+        <v>1.78</v>
+      </c>
+      <c r="E37">
+        <f ca="1"/>
+        <v>55</v>
+      </c>
+      <c r="F37">
+        <f ca="1"/>
+        <v>121.25</v>
+      </c>
+      <c r="G37">
+        <f ca="1"/>
+        <v>17.35891932836763</v>
+      </c>
+      <c r="H37">
+        <f ca="1"/>
+        <v>-15.971146351467677</v>
+      </c>
+      <c r="I37">
+        <f ca="1"/>
+        <v>52</v>
+      </c>
+      <c r="J37" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K37" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="L37" t="str">
+        <f ca="1"/>
+        <v>hazel</v>
+      </c>
+      <c r="M37">
+        <f ca="1"/>
+        <v>48</v>
+      </c>
+      <c r="N37" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <f ca="1"/>
+        <v>17520</v>
+      </c>
+      <c r="P37">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" t="str">
+        <f ca="1"/>
+        <v>Ryloth</v>
+      </c>
+      <c r="R37" t="str">
+        <f ca="1"/>
+        <v>Twi'lek</v>
+      </c>
+      <c r="S37" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve"> Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U37" s="15">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="V37" s="4" cm="1">
+        <f t="array" aca="1" ref="V37" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>4</v>
+      </c>
+      <c r="W37" s="15">
+        <f ca="1"/>
+        <v>178</v>
+      </c>
+      <c r="X37" cm="1">
+        <f t="array" aca="1" ref="X37" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-3.6419753086419746</v>
+      </c>
+      <c r="Y37" cm="1">
+        <f t="array" aca="1" ref="Y37" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>13.263984148757807</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
+      <c r="A38" t="str">
+        <f ca="1"/>
+        <v>Shaak Ti</v>
+      </c>
+      <c r="B38">
+        <f ca="1"/>
+        <v>178</v>
+      </c>
+      <c r="C38">
+        <f ca="1"/>
+        <v>70</v>
+      </c>
+      <c r="D38">
+        <f ca="1"/>
+        <v>1.78</v>
+      </c>
+      <c r="E38">
+        <f ca="1"/>
+        <v>57</v>
+      </c>
+      <c r="F38">
+        <f ca="1"/>
+        <v>125.5</v>
+      </c>
+      <c r="G38">
+        <f ca="1"/>
+        <v>17.99015275849009</v>
+      </c>
+      <c r="H38">
+        <f ca="1"/>
+        <v>-15.339912921345217</v>
+      </c>
+      <c r="I38">
+        <f ca="1"/>
+        <v>51</v>
+      </c>
+      <c r="J38" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K38" t="str">
+        <f ca="1"/>
+        <v>red, blue, white</v>
+      </c>
+      <c r="L38" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="M38" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N38" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O38" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P38">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" t="str">
+        <f ca="1"/>
+        <v>Shili</v>
+      </c>
+      <c r="R38" t="str">
+        <f ca="1"/>
+        <v>Togruta</v>
+      </c>
+      <c r="S38" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T38" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Revenge of the Sith </v>
+      </c>
+      <c r="U38" s="15">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="V38" s="4" cm="1">
+        <f t="array" aca="1" ref="V38" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>4</v>
+      </c>
+      <c r="W38" s="15">
+        <f ca="1"/>
+        <v>178</v>
+      </c>
+      <c r="X38" cm="1">
+        <f t="array" aca="1" ref="X38" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-3.6419753086419746</v>
+      </c>
+      <c r="Y38" cm="1">
+        <f t="array" aca="1" ref="Y38" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>13.263984148757807</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
+      <c r="A39" t="str">
+        <f ca="1"/>
+        <v>Sly Moore</v>
+      </c>
+      <c r="B39">
+        <f ca="1"/>
+        <v>178</v>
+      </c>
+      <c r="C39">
+        <f ca="1"/>
+        <v>70</v>
+      </c>
+      <c r="D39">
+        <f ca="1"/>
+        <v>1.78</v>
+      </c>
+      <c r="E39">
+        <f ca="1"/>
+        <v>48</v>
+      </c>
+      <c r="F39">
+        <f ca="1"/>
+        <v>105.75</v>
+      </c>
+      <c r="G39">
+        <f ca="1"/>
+        <v>15.149602322939023</v>
+      </c>
+      <c r="H39">
+        <f ca="1"/>
+        <v>-18.180463356896283</v>
+      </c>
+      <c r="I39">
+        <f ca="1"/>
+        <v>57</v>
+      </c>
+      <c r="J39" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K39" t="str">
+        <f ca="1"/>
+        <v>pale</v>
+      </c>
+      <c r="L39" t="str">
+        <f ca="1"/>
+        <v>white</v>
+      </c>
+      <c r="M39" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N39" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O39" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P39">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q39" t="str">
+        <f ca="1"/>
+        <v>Umbara</v>
+      </c>
+      <c r="R39" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="S39" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T39" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Revenge of the Sith </v>
+      </c>
+      <c r="U39" s="15">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="V39" s="4" cm="1">
+        <f t="array" aca="1" ref="V39" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>4</v>
+      </c>
+      <c r="W39" s="15">
+        <f ca="1"/>
+        <v>178</v>
+      </c>
+      <c r="X39" cm="1">
+        <f t="array" aca="1" ref="X39" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-3.6419753086419746</v>
+      </c>
+      <c r="Y39" cm="1">
+        <f t="array" aca="1" ref="Y39" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>13.263984148757807</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
+      <c r="A40" t="str">
+        <f ca="1"/>
+        <v>Wilhuff Tarkin</v>
+      </c>
+      <c r="B40">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="C40">
+        <f ca="1"/>
+        <v>70.5</v>
+      </c>
+      <c r="D40">
+        <f ca="1"/>
+        <v>1.8</v>
+      </c>
+      <c r="E40" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F40" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G40">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I40">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J40" t="str">
+        <f ca="1"/>
+        <v>auburn, grey</v>
+      </c>
+      <c r="K40" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L40" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M40">
+        <f ca="1"/>
+        <v>64</v>
+      </c>
+      <c r="N40" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O40">
+        <f ca="1"/>
+        <v>23360</v>
+      </c>
+      <c r="P40">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" t="str">
+        <f ca="1"/>
+        <v>Eriadu</v>
+      </c>
+      <c r="R40" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S40" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T40" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Revenge of the Sith ,  A New Hope </v>
+      </c>
+      <c r="U40" s="15">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="V40" s="4" cm="1">
+        <f t="array" aca="1" ref="V40" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W40" s="15">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="X40" cm="1">
+        <f t="array" aca="1" ref="X40" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-5.6419753086419746</v>
+      </c>
+      <c r="Y40" cm="1">
+        <f t="array" aca="1" ref="Y40" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>31.831885383325705</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
+      <c r="A41" t="str">
+        <f ca="1"/>
+        <v>Han Solo</v>
+      </c>
+      <c r="B41">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="C41">
+        <f ca="1"/>
+        <v>70.5</v>
+      </c>
+      <c r="D41">
+        <f ca="1"/>
+        <v>1.8</v>
+      </c>
+      <c r="E41">
+        <f ca="1"/>
+        <v>80</v>
+      </c>
+      <c r="F41">
+        <f ca="1"/>
+        <v>176.25</v>
+      </c>
+      <c r="G41">
+        <f ca="1"/>
+        <v>24.691358024691358</v>
+      </c>
+      <c r="H41">
+        <f ca="1"/>
+        <v>-8.6387076551439499</v>
+      </c>
+      <c r="I41">
+        <f ca="1"/>
+        <v>29</v>
+      </c>
+      <c r="J41" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K41" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L41" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M41">
+        <f ca="1"/>
+        <v>29</v>
+      </c>
+      <c r="N41" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O41">
+        <f ca="1"/>
+        <v>10585</v>
+      </c>
+      <c r="P41">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" t="str">
+        <f ca="1"/>
+        <v>Corellia</v>
+      </c>
+      <c r="R41" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S41" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="T41" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Return of the Jedi ,  The Empire Strikes Back ,  A New Hope ,  The Force Awakens </v>
+      </c>
+      <c r="U41" s="15">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="V41" s="4" cm="1">
+        <f t="array" aca="1" ref="V41" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W41" s="15">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="X41" cm="1">
+        <f t="array" aca="1" ref="X41" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-5.6419753086419746</v>
+      </c>
+      <c r="Y41" cm="1">
+        <f t="array" aca="1" ref="Y41" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>31.831885383325705</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
+      <c r="A42" t="str">
+        <f ca="1"/>
+        <v>Jek Tono Porkins</v>
+      </c>
+      <c r="B42">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="C42">
+        <f ca="1"/>
+        <v>70.5</v>
+      </c>
+      <c r="D42">
+        <f ca="1"/>
+        <v>1.8</v>
+      </c>
+      <c r="E42">
+        <f ca="1"/>
+        <v>110</v>
+      </c>
+      <c r="F42">
+        <f ca="1"/>
+        <v>242.5</v>
+      </c>
+      <c r="G42">
+        <f ca="1"/>
+        <v>33.950617283950614</v>
+      </c>
+      <c r="H42">
+        <f ca="1"/>
+        <v>0.62055160411530608</v>
+      </c>
+      <c r="I42">
+        <f ca="1"/>
+        <v>9</v>
+      </c>
+      <c r="J42" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K42" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L42" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M42" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N42" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O42" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P42">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" t="str">
+        <f ca="1"/>
+        <v>Bestine IV</v>
+      </c>
+      <c r="R42" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S42" t="str">
+        <f ca="1"/>
+        <v>A New Hope</v>
+      </c>
+      <c r="T42" t="str">
+        <f ca="1"/>
+        <v>A New Hope</v>
+      </c>
+      <c r="U42" s="15">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="V42" s="4" cm="1">
+        <f t="array" aca="1" ref="V42" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W42" s="15">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="X42" cm="1">
+        <f t="array" aca="1" ref="X42" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-5.6419753086419746</v>
+      </c>
+      <c r="Y42" cm="1">
+        <f t="array" aca="1" ref="Y42" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>31.831885383325705</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
+      <c r="A43" t="str">
+        <f ca="1"/>
+        <v>Ackbar</v>
+      </c>
+      <c r="B43">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="C43">
+        <f ca="1"/>
+        <v>70.5</v>
+      </c>
+      <c r="D43">
+        <f ca="1"/>
+        <v>1.8</v>
+      </c>
+      <c r="E43">
+        <f ca="1"/>
+        <v>83</v>
+      </c>
+      <c r="F43">
+        <f ca="1"/>
+        <v>182.75</v>
+      </c>
+      <c r="G43">
+        <f ca="1"/>
+        <v>25.617283950617281</v>
+      </c>
+      <c r="H43">
+        <f ca="1"/>
+        <v>-7.7127817292180261</v>
+      </c>
+      <c r="I43">
+        <f ca="1"/>
+        <v>23</v>
+      </c>
+      <c r="J43" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K43" t="str">
+        <f ca="1"/>
+        <v>brown mottle</v>
+      </c>
+      <c r="L43" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="M43">
+        <f ca="1"/>
+        <v>41</v>
+      </c>
+      <c r="N43" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <f ca="1"/>
+        <v>14965</v>
+      </c>
+      <c r="P43">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q43" t="str">
+        <f ca="1"/>
+        <v>Mon Cala</v>
+      </c>
+      <c r="R43" t="str">
+        <f ca="1"/>
+        <v>Mon Calamari</v>
+      </c>
+      <c r="S43" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="T43" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Return of the Jedi ,  The Force Awakens </v>
+      </c>
+      <c r="U43" s="15">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="V43" s="4" cm="1">
+        <f t="array" aca="1" ref="V43" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W43" s="15">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="X43" cm="1">
+        <f t="array" aca="1" ref="X43" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-5.6419753086419746</v>
+      </c>
+      <c r="Y43" cm="1">
+        <f t="array" aca="1" ref="Y43" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>31.831885383325705</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
+      <c r="A44" t="str">
+        <f ca="1"/>
+        <v>Bib Fortuna</v>
+      </c>
+      <c r="B44">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="C44">
+        <f ca="1"/>
+        <v>70.5</v>
+      </c>
+      <c r="D44">
+        <f ca="1"/>
+        <v>1.8</v>
+      </c>
+      <c r="E44" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F44" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G44">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I44">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J44" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K44" t="str">
+        <f ca="1"/>
+        <v>pale</v>
+      </c>
+      <c r="L44" t="str">
+        <f ca="1"/>
+        <v>pink</v>
+      </c>
+      <c r="M44" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N44" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O44" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P44">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="str">
+        <f ca="1"/>
+        <v>Ryloth</v>
+      </c>
+      <c r="R44" t="str">
+        <f ca="1"/>
+        <v>Twi'lek</v>
+      </c>
+      <c r="S44" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="T44" t="str">
+        <f ca="1"/>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="U44" s="15">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="V44" s="4" cm="1">
+        <f t="array" aca="1" ref="V44" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W44" s="15">
+        <f ca="1"/>
+        <v>180</v>
+      </c>
+      <c r="X44" cm="1">
+        <f t="array" aca="1" ref="X44" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-5.6419753086419746</v>
+      </c>
+      <c r="Y44" cm="1">
+        <f t="array" aca="1" ref="Y44" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>31.831885383325705</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
+      <c r="A45" t="str">
+        <f ca="1"/>
+        <v>Obi-Wan Kenobi</v>
+      </c>
+      <c r="B45">
+        <f ca="1"/>
+        <v>182</v>
+      </c>
+      <c r="C45">
+        <f ca="1"/>
+        <v>71.5</v>
+      </c>
+      <c r="D45">
+        <f ca="1"/>
+        <v>1.82</v>
+      </c>
+      <c r="E45">
+        <f ca="1"/>
+        <v>77</v>
+      </c>
+      <c r="F45">
+        <f ca="1"/>
+        <v>169.75</v>
+      </c>
+      <c r="G45">
+        <f ca="1"/>
+        <v>23.245984784446321</v>
+      </c>
+      <c r="H45">
+        <f ca="1"/>
+        <v>-10.084080895388986</v>
+      </c>
+      <c r="I45">
+        <f ca="1"/>
+        <v>39</v>
+      </c>
+      <c r="J45" t="str">
+        <f ca="1"/>
+        <v>auburn, white</v>
+      </c>
+      <c r="K45" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L45" t="str">
+        <f ca="1"/>
+        <v>blue-gray</v>
+      </c>
+      <c r="M45">
+        <f ca="1"/>
+        <v>57</v>
+      </c>
+      <c r="N45" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O45">
+        <f ca="1"/>
+        <v>20805</v>
+      </c>
+      <c r="P45">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q45" t="str">
+        <f ca="1"/>
+        <v>Stewjon</v>
+      </c>
+      <c r="R45" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S45" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T45" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith ,  Return of the Jedi ,  The Empire Strikes Back ,  A New Hope </v>
+      </c>
+      <c r="U45" s="15">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="V45" s="4" cm="1">
+        <f t="array" aca="1" ref="V45" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W45" s="15">
+        <f ca="1"/>
+        <v>182</v>
+      </c>
+      <c r="X45" cm="1">
+        <f t="array" aca="1" ref="X45" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-7.6419753086419746</v>
+      </c>
+      <c r="Y45" cm="1">
+        <f t="array" aca="1" ref="Y45" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>58.399786617893604</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25">
+      <c r="A46" t="str">
+        <f ca="1"/>
+        <v>Biggs Darklighter</v>
+      </c>
+      <c r="B46">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="C46">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="D46">
+        <f ca="1"/>
+        <v>1.83</v>
+      </c>
+      <c r="E46">
+        <f ca="1"/>
+        <v>84</v>
+      </c>
+      <c r="F46">
+        <f ca="1"/>
+        <v>185</v>
+      </c>
+      <c r="G46">
+        <f ca="1"/>
+        <v>25.082863029651524</v>
+      </c>
+      <c r="H46">
+        <f ca="1"/>
+        <v>-8.2472026501837838</v>
+      </c>
+      <c r="I46">
+        <f ca="1"/>
+        <v>25</v>
+      </c>
+      <c r="J46" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K46" t="str">
+        <f ca="1"/>
+        <v>light</v>
+      </c>
+      <c r="L46" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M46">
+        <f ca="1"/>
+        <v>24</v>
+      </c>
+      <c r="N46" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O46">
+        <f ca="1"/>
+        <v>8760</v>
+      </c>
+      <c r="P46">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R46" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S46" t="str">
+        <f ca="1"/>
+        <v>A New Hope</v>
+      </c>
+      <c r="T46" t="str">
+        <f ca="1"/>
+        <v>A New Hope</v>
+      </c>
+      <c r="U46" s="15">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="V46" s="4" cm="1">
+        <f t="array" aca="1" ref="V46" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>7</v>
+      </c>
+      <c r="W46" s="15">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="X46" cm="1">
+        <f t="array" aca="1" ref="X46" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-8.6419753086419746</v>
+      </c>
+      <c r="Y46" cm="1">
+        <f t="array" aca="1" ref="Y46" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>74.683737235177546</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25">
+      <c r="A47" t="str">
+        <f ca="1"/>
+        <v>Boba Fett</v>
+      </c>
+      <c r="B47">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="C47">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="D47">
+        <f ca="1"/>
+        <v>1.83</v>
+      </c>
+      <c r="E47">
+        <f ca="1"/>
+        <v>78.2</v>
+      </c>
+      <c r="F47">
+        <f ca="1"/>
+        <v>172.25</v>
+      </c>
+      <c r="G47">
+        <f ca="1"/>
+        <v>23.350951058556539</v>
+      </c>
+      <c r="H47">
+        <f ca="1"/>
+        <v>-9.979114621278768</v>
+      </c>
+      <c r="I47">
+        <f ca="1"/>
+        <v>38</v>
+      </c>
+      <c r="J47" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K47" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L47" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M47">
+        <f ca="1"/>
+        <v>31.5</v>
+      </c>
+      <c r="N47" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O47">
+        <f ca="1"/>
+        <v>11497.5</v>
+      </c>
+      <c r="P47">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q47" t="str">
+        <f ca="1"/>
+        <v>Kamino</v>
+      </c>
+      <c r="R47" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S47" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T47" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Return of the Jedi ,  The Empire Strikes Back </v>
+      </c>
+      <c r="U47" s="15">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="V47" s="4" cm="1">
+        <f t="array" aca="1" ref="V47" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>7</v>
+      </c>
+      <c r="W47" s="15">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="X47" cm="1">
+        <f t="array" aca="1" ref="X47" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-8.6419753086419746</v>
+      </c>
+      <c r="Y47" cm="1">
+        <f t="array" aca="1" ref="Y47" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>74.683737235177546</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25">
+      <c r="A48" t="str">
+        <f ca="1"/>
+        <v>Ric Olié</v>
+      </c>
+      <c r="B48">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="C48">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="D48">
+        <f ca="1"/>
+        <v>1.83</v>
+      </c>
+      <c r="E48" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F48" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G48">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I48">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J48" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K48" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L48" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M48" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N48" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O48" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P48">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R48" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="S48" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T48" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U48" s="15">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="V48" s="4" cm="1">
+        <f t="array" aca="1" ref="V48" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>7</v>
+      </c>
+      <c r="W48" s="15">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="X48" cm="1">
+        <f t="array" aca="1" ref="X48" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-8.6419753086419746</v>
+      </c>
+      <c r="Y48" cm="1">
+        <f t="array" aca="1" ref="Y48" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>74.683737235177546</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25">
+      <c r="A49" t="str">
+        <f ca="1"/>
+        <v>Quarsh Panaka</v>
+      </c>
+      <c r="B49">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="C49">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="D49">
+        <f ca="1"/>
+        <v>1.83</v>
+      </c>
+      <c r="E49" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F49" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G49">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I49">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J49" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K49" t="str">
+        <f ca="1"/>
+        <v>dark</v>
+      </c>
+      <c r="L49" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M49">
+        <f ca="1"/>
+        <v>62</v>
+      </c>
+      <c r="N49" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O49">
+        <f ca="1"/>
+        <v>22630</v>
+      </c>
+      <c r="P49">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R49" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="S49" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T49" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U49" s="15">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="V49" s="4" cm="1">
+        <f t="array" aca="1" ref="V49" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>7</v>
+      </c>
+      <c r="W49" s="15">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="X49" cm="1">
+        <f t="array" aca="1" ref="X49" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-8.6419753086419746</v>
+      </c>
+      <c r="Y49" cm="1">
+        <f t="array" aca="1" ref="Y49" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>74.683737235177546</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25">
+      <c r="A50" t="str">
+        <f ca="1"/>
+        <v>Cliegg Lars</v>
+      </c>
+      <c r="B50">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="C50">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="D50">
+        <f ca="1"/>
+        <v>1.83</v>
+      </c>
+      <c r="E50" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F50" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G50">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I50">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J50" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K50" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L50" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M50">
+        <f ca="1"/>
+        <v>82</v>
+      </c>
+      <c r="N50" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <f ca="1"/>
+        <v>29930</v>
+      </c>
+      <c r="P50">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q50" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R50" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S50" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T50" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U50" s="15">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="V50" s="4" cm="1">
+        <f t="array" aca="1" ref="V50" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>7</v>
+      </c>
+      <c r="W50" s="15">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="X50" cm="1">
+        <f t="array" aca="1" ref="X50" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-8.6419753086419746</v>
+      </c>
+      <c r="Y50" cm="1">
+        <f t="array" aca="1" ref="Y50" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>74.683737235177546</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" t="str">
+        <f ca="1"/>
+        <v>Poggle the Lesser</v>
+      </c>
+      <c r="B51">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="C51">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="D51">
+        <f ca="1"/>
+        <v>1.83</v>
+      </c>
+      <c r="E51">
+        <f ca="1"/>
+        <v>80</v>
+      </c>
+      <c r="F51">
+        <f ca="1"/>
+        <v>176.25</v>
+      </c>
+      <c r="G51">
+        <f ca="1"/>
+        <v>23.888440980620498</v>
+      </c>
+      <c r="H51">
+        <f ca="1"/>
+        <v>-9.4416246992148096</v>
+      </c>
+      <c r="I51">
+        <f ca="1"/>
+        <v>34</v>
+      </c>
+      <c r="J51" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K51" t="str">
+        <f ca="1"/>
+        <v>green</v>
+      </c>
+      <c r="L51" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M51" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N51" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O51" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P51">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q51" t="str">
+        <f ca="1"/>
+        <v>Geonosis</v>
+      </c>
+      <c r="R51" t="str">
+        <f ca="1"/>
+        <v>Geonosian</v>
+      </c>
+      <c r="S51" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T51" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Revenge of the Sith </v>
+      </c>
+      <c r="U51" s="15">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="V51" s="4" cm="1">
+        <f t="array" aca="1" ref="V51" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>7</v>
+      </c>
+      <c r="W51" s="15">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="X51" cm="1">
+        <f t="array" aca="1" ref="X51" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-8.6419753086419746</v>
+      </c>
+      <c r="Y51" cm="1">
+        <f t="array" aca="1" ref="Y51" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>74.683737235177546</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25">
+      <c r="A52" t="str">
+        <f ca="1"/>
+        <v>Jango Fett</v>
+      </c>
+      <c r="B52">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="C52">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="D52">
+        <f ca="1"/>
+        <v>1.83</v>
+      </c>
+      <c r="E52">
+        <f ca="1"/>
+        <v>79</v>
+      </c>
+      <c r="F52">
+        <f ca="1"/>
+        <v>174</v>
+      </c>
+      <c r="G52">
+        <f ca="1"/>
+        <v>23.589835468362743</v>
+      </c>
+      <c r="H52">
+        <f ca="1"/>
+        <v>-9.7402302114725643</v>
+      </c>
+      <c r="I52">
+        <f ca="1"/>
+        <v>37</v>
+      </c>
+      <c r="J52" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K52" t="str">
+        <f ca="1"/>
+        <v>tan</v>
+      </c>
+      <c r="L52" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M52">
+        <f ca="1"/>
+        <v>66</v>
+      </c>
+      <c r="N52" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O52">
+        <f ca="1"/>
+        <v>24090</v>
+      </c>
+      <c r="P52">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q52" t="str">
+        <f ca="1"/>
+        <v>Concord Dawn</v>
+      </c>
+      <c r="R52" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S52" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T52" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U52" s="15">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="V52" s="4" cm="1">
+        <f t="array" aca="1" ref="V52" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>7</v>
+      </c>
+      <c r="W52" s="15">
+        <f ca="1"/>
+        <v>183</v>
+      </c>
+      <c r="X52" cm="1">
+        <f t="array" aca="1" ref="X52" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-8.6419753086419746</v>
+      </c>
+      <c r="Y52" cm="1">
+        <f t="array" aca="1" ref="Y52" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>74.683737235177546</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25">
+      <c r="A53" t="str">
+        <f ca="1"/>
+        <v>Adi Gallia</v>
+      </c>
+      <c r="B53">
+        <f ca="1"/>
+        <v>184</v>
+      </c>
+      <c r="C53">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="D53">
+        <f ca="1"/>
+        <v>1.84</v>
+      </c>
+      <c r="E53">
+        <f ca="1"/>
+        <v>50</v>
+      </c>
+      <c r="F53">
+        <f ca="1"/>
+        <v>110</v>
+      </c>
+      <c r="G53">
+        <f ca="1"/>
+        <v>14.768431001890358</v>
+      </c>
+      <c r="H53">
+        <f ca="1"/>
+        <v>-18.561634677944951</v>
+      </c>
+      <c r="I53">
+        <f ca="1"/>
+        <v>58</v>
+      </c>
+      <c r="J53" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K53" t="str">
+        <f ca="1"/>
+        <v>dark</v>
+      </c>
+      <c r="L53" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M53" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N53" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O53" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P53">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q53" t="str">
+        <f ca="1"/>
+        <v>Coruscant</v>
+      </c>
+      <c r="R53" t="str">
+        <f ca="1"/>
+        <v>Tholothian</v>
+      </c>
+      <c r="S53" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T53" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U53" s="15">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="V53" s="4" cm="1">
+        <f t="array" aca="1" ref="V53" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W53" s="15">
+        <f ca="1"/>
+        <v>184</v>
+      </c>
+      <c r="X53" cm="1">
+        <f t="array" aca="1" ref="X53" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-9.6419753086419746</v>
+      </c>
+      <c r="Y53" cm="1">
+        <f t="array" aca="1" ref="Y53" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>92.967687852461495</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25">
+      <c r="A54" t="str">
+        <f ca="1"/>
+        <v>Gregar Typho</v>
+      </c>
+      <c r="B54">
+        <f ca="1"/>
+        <v>185</v>
+      </c>
+      <c r="C54">
+        <f ca="1"/>
+        <v>72.5</v>
+      </c>
+      <c r="D54">
+        <f ca="1"/>
+        <v>1.85</v>
+      </c>
+      <c r="E54">
+        <f ca="1"/>
+        <v>85</v>
+      </c>
+      <c r="F54">
+        <f ca="1"/>
+        <v>187.25</v>
+      </c>
+      <c r="G54">
+        <f ca="1"/>
+        <v>24.835646457268076</v>
+      </c>
+      <c r="H54">
+        <f ca="1"/>
+        <v>-8.494419222567231</v>
+      </c>
+      <c r="I54">
+        <f ca="1"/>
+        <v>27</v>
+      </c>
+      <c r="J54" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K54" t="str">
+        <f ca="1"/>
+        <v>dark</v>
+      </c>
+      <c r="L54" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M54" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N54" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O54" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P54">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q54" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R54" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S54" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T54" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U54" s="15">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="V54" s="4" cm="1">
+        <f t="array" aca="1" ref="V54" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W54" s="15">
+        <f ca="1"/>
+        <v>185</v>
+      </c>
+      <c r="X54" cm="1">
+        <f t="array" aca="1" ref="X54" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-10.641975308641975</v>
+      </c>
+      <c r="Y54" cm="1">
+        <f t="array" aca="1" ref="Y54" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>113.25163846974544</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25">
+      <c r="A55" t="str">
+        <f ca="1"/>
+        <v>Anakin Skywalker</v>
+      </c>
+      <c r="B55">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="C55">
+        <f ca="1"/>
+        <v>74</v>
+      </c>
+      <c r="D55">
+        <f ca="1"/>
+        <v>1.88</v>
+      </c>
+      <c r="E55">
+        <f ca="1"/>
+        <v>84</v>
+      </c>
+      <c r="F55">
+        <f ca="1"/>
+        <v>185</v>
+      </c>
+      <c r="G55">
+        <f ca="1"/>
+        <v>23.766410140334994</v>
+      </c>
+      <c r="H55">
+        <f ca="1"/>
+        <v>-9.5636555395003136</v>
+      </c>
+      <c r="I55">
+        <f ca="1"/>
+        <v>35</v>
+      </c>
+      <c r="J55" t="str">
+        <f ca="1"/>
+        <v>blond</v>
+      </c>
+      <c r="K55" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L55" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M55">
+        <f ca="1"/>
+        <v>41.9</v>
+      </c>
+      <c r="N55" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O55">
+        <f ca="1"/>
+        <v>15293.5</v>
+      </c>
+      <c r="P55">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q55" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R55" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S55" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T55" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U55" s="15">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="V55" s="4" cm="1">
+        <f t="array" aca="1" ref="V55" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W55" s="15">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="X55" cm="1">
+        <f t="array" aca="1" ref="X55" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-13.641975308641975</v>
+      </c>
+      <c r="Y55" cm="1">
+        <f t="array" aca="1" ref="Y55" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>186.10349032159729</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25">
+      <c r="A56" t="str">
+        <f ca="1"/>
+        <v>Mace Windu</v>
+      </c>
+      <c r="B56">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="C56">
+        <f ca="1"/>
+        <v>74</v>
+      </c>
+      <c r="D56">
+        <f ca="1"/>
+        <v>1.88</v>
+      </c>
+      <c r="E56">
+        <f ca="1"/>
+        <v>84</v>
+      </c>
+      <c r="F56">
+        <f ca="1"/>
+        <v>185</v>
+      </c>
+      <c r="G56">
+        <f ca="1"/>
+        <v>23.766410140334994</v>
+      </c>
+      <c r="H56">
+        <f ca="1"/>
+        <v>-9.5636555395003136</v>
+      </c>
+      <c r="I56">
+        <f ca="1"/>
+        <v>35</v>
+      </c>
+      <c r="J56" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K56" t="str">
+        <f ca="1"/>
+        <v>dark</v>
+      </c>
+      <c r="L56" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M56">
+        <f ca="1"/>
+        <v>72</v>
+      </c>
+      <c r="N56" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <f ca="1"/>
+        <v>26280</v>
+      </c>
+      <c r="P56">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q56" t="str">
+        <f ca="1"/>
+        <v>Haruun Kal</v>
+      </c>
+      <c r="R56" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S56" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T56" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U56" s="15">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="V56" s="4" cm="1">
+        <f t="array" aca="1" ref="V56" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W56" s="15">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="X56" cm="1">
+        <f t="array" aca="1" ref="X56" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-13.641975308641975</v>
+      </c>
+      <c r="Y56" cm="1">
+        <f t="array" aca="1" ref="Y56" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>186.10349032159729</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25">
+      <c r="A57" t="str">
+        <f ca="1"/>
+        <v>Saesee Tiin</v>
+      </c>
+      <c r="B57">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="C57">
+        <f ca="1"/>
+        <v>74</v>
+      </c>
+      <c r="D57">
+        <f ca="1"/>
+        <v>1.88</v>
+      </c>
+      <c r="E57" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F57" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G57">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I57">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J57" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K57" t="str">
+        <f ca="1"/>
+        <v>pale</v>
+      </c>
+      <c r="L57" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="M57" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N57" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O57" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P57">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" t="str">
+        <f ca="1"/>
+        <v>Iktotch</v>
+      </c>
+      <c r="R57" t="str">
+        <f ca="1"/>
+        <v>Iktotchi</v>
+      </c>
+      <c r="S57" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T57" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U57" s="15">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="V57" s="4" cm="1">
+        <f t="array" aca="1" ref="V57" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W57" s="15">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="X57" cm="1">
+        <f t="array" aca="1" ref="X57" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-13.641975308641975</v>
+      </c>
+      <c r="Y57" cm="1">
+        <f t="array" aca="1" ref="Y57" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>186.10349032159729</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25">
+      <c r="A58" t="str">
+        <f ca="1"/>
+        <v>Plo Koon</v>
+      </c>
+      <c r="B58">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="C58">
+        <f ca="1"/>
+        <v>74</v>
+      </c>
+      <c r="D58">
+        <f ca="1"/>
+        <v>1.88</v>
+      </c>
+      <c r="E58">
+        <f ca="1"/>
+        <v>80</v>
+      </c>
+      <c r="F58">
+        <f ca="1"/>
+        <v>176.25</v>
+      </c>
+      <c r="G58">
+        <f ca="1"/>
+        <v>22.634676324128566</v>
+      </c>
+      <c r="H58">
+        <f ca="1"/>
+        <v>-10.695389355706741</v>
+      </c>
+      <c r="I58">
+        <f ca="1"/>
+        <v>41</v>
+      </c>
+      <c r="J58" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K58" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="L58" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="M58">
+        <f ca="1"/>
+        <v>22</v>
+      </c>
+      <c r="N58" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <f ca="1"/>
+        <v>8030</v>
+      </c>
+      <c r="P58">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" t="str">
+        <f ca="1"/>
+        <v>Dorin</v>
+      </c>
+      <c r="R58" t="str">
+        <f ca="1"/>
+        <v>Kel Dor</v>
+      </c>
+      <c r="S58" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T58" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U58" s="15">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="V58" s="4" cm="1">
+        <f t="array" aca="1" ref="V58" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W58" s="15">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="X58" cm="1">
+        <f t="array" aca="1" ref="X58" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-13.641975308641975</v>
+      </c>
+      <c r="Y58" cm="1">
+        <f t="array" aca="1" ref="Y58" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>186.10349032159729</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25">
+      <c r="A59" t="str">
+        <f ca="1"/>
+        <v>Raymus Antilles</v>
+      </c>
+      <c r="B59">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="C59">
+        <f ca="1"/>
+        <v>74</v>
+      </c>
+      <c r="D59">
+        <f ca="1"/>
+        <v>1.88</v>
+      </c>
+      <c r="E59">
+        <f ca="1"/>
+        <v>79</v>
+      </c>
+      <c r="F59">
+        <f ca="1"/>
+        <v>174</v>
+      </c>
+      <c r="G59">
+        <f ca="1"/>
+        <v>22.351742870076958</v>
+      </c>
+      <c r="H59">
+        <f ca="1"/>
+        <v>-10.97832280975835</v>
+      </c>
+      <c r="I59">
+        <f ca="1"/>
+        <v>42</v>
+      </c>
+      <c r="J59" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K59" t="str">
+        <f ca="1"/>
+        <v>light</v>
+      </c>
+      <c r="L59" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M59" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N59" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O59" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P59">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q59" t="str">
+        <f ca="1"/>
+        <v>Alderaan</v>
+      </c>
+      <c r="R59" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S59" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T59" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Revenge of the Sith ,  A New Hope </v>
+      </c>
+      <c r="U59" s="15">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="V59" s="4" cm="1">
+        <f t="array" aca="1" ref="V59" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>5</v>
+      </c>
+      <c r="W59" s="15">
+        <f ca="1"/>
+        <v>188</v>
+      </c>
+      <c r="X59" cm="1">
+        <f t="array" aca="1" ref="X59" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-13.641975308641975</v>
+      </c>
+      <c r="Y59" cm="1">
+        <f t="array" aca="1" ref="Y59" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>186.10349032159729</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25">
+      <c r="A60" t="str">
+        <f ca="1"/>
+        <v>Bossk</v>
+      </c>
+      <c r="B60">
+        <f ca="1"/>
+        <v>190</v>
+      </c>
+      <c r="C60">
+        <f ca="1"/>
+        <v>74.5</v>
+      </c>
+      <c r="D60">
+        <f ca="1"/>
+        <v>1.9</v>
+      </c>
+      <c r="E60">
+        <f ca="1"/>
+        <v>113</v>
+      </c>
+      <c r="F60">
+        <f ca="1"/>
+        <v>249</v>
+      </c>
+      <c r="G60">
+        <f ca="1"/>
+        <v>31.301939058171747</v>
+      </c>
+      <c r="H60">
+        <f ca="1"/>
+        <v>-2.0281266216635601</v>
+      </c>
+      <c r="I60">
+        <f ca="1"/>
+        <v>12</v>
+      </c>
+      <c r="J60" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K60" t="str">
+        <f ca="1"/>
+        <v>green</v>
+      </c>
+      <c r="L60" t="str">
+        <f ca="1"/>
+        <v>red</v>
+      </c>
+      <c r="M60">
+        <f ca="1"/>
+        <v>53</v>
+      </c>
+      <c r="N60" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O60">
+        <f ca="1"/>
+        <v>19345</v>
+      </c>
+      <c r="P60">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" t="str">
+        <f ca="1"/>
+        <v>Trandosha</v>
+      </c>
+      <c r="R60" t="str">
+        <f ca="1"/>
+        <v>Trandoshan</v>
+      </c>
+      <c r="S60" t="str">
+        <f ca="1"/>
+        <v>The Empire Strikes Back</v>
+      </c>
+      <c r="T60" t="str">
+        <f ca="1"/>
+        <v>The Empire Strikes Back</v>
+      </c>
+      <c r="U60" s="15">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="V60" s="4" cm="1">
+        <f t="array" aca="1" ref="V60" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W60" s="15">
+        <f ca="1"/>
+        <v>190</v>
+      </c>
+      <c r="X60" cm="1">
+        <f t="array" aca="1" ref="X60" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-15.641975308641975</v>
+      </c>
+      <c r="Y60" cm="1">
+        <f t="array" aca="1" ref="Y60" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>244.67139155616519</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25">
+      <c r="A61" t="str">
+        <f ca="1"/>
+        <v>Nute Gunray</v>
+      </c>
+      <c r="B61">
+        <f ca="1"/>
+        <v>191</v>
+      </c>
+      <c r="C61">
+        <f ca="1"/>
+        <v>75</v>
+      </c>
+      <c r="D61">
+        <f ca="1"/>
+        <v>1.91</v>
+      </c>
+      <c r="E61">
+        <f ca="1"/>
+        <v>90</v>
+      </c>
+      <c r="F61">
+        <f ca="1"/>
+        <v>198.25</v>
+      </c>
+      <c r="G61">
+        <f ca="1"/>
+        <v>24.670376360297141</v>
+      </c>
+      <c r="H61">
+        <f ca="1"/>
+        <v>-8.6596893195381668</v>
+      </c>
+      <c r="I61">
+        <f ca="1"/>
+        <v>30</v>
+      </c>
+      <c r="J61" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K61" t="str">
+        <f ca="1"/>
+        <v>mottled green</v>
+      </c>
+      <c r="L61" t="str">
+        <f ca="1"/>
+        <v>red</v>
+      </c>
+      <c r="M61" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N61" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O61" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P61">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q61" t="str">
+        <f ca="1"/>
+        <v>Cato Neimoidia</v>
+      </c>
+      <c r="R61" t="str">
+        <f ca="1"/>
+        <v>Neimodian</v>
+      </c>
+      <c r="S61" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T61" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U61" s="15">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="V61" s="4" cm="1">
+        <f t="array" aca="1" ref="V61" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W61" s="15">
+        <f ca="1"/>
+        <v>191</v>
+      </c>
+      <c r="X61" cm="1">
+        <f t="array" aca="1" ref="X61" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-16.641975308641975</v>
+      </c>
+      <c r="Y61" cm="1">
+        <f t="array" aca="1" ref="Y61" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>276.95534217344914</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25">
+      <c r="A62" t="str">
+        <f ca="1"/>
+        <v>Bail Prestor Organa</v>
+      </c>
+      <c r="B62">
+        <f ca="1"/>
+        <v>191</v>
+      </c>
+      <c r="C62">
+        <f ca="1"/>
+        <v>75</v>
+      </c>
+      <c r="D62">
+        <f ca="1"/>
+        <v>1.91</v>
+      </c>
+      <c r="E62" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F62" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G62">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I62">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J62" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="K62" t="str">
+        <f ca="1"/>
+        <v>tan</v>
+      </c>
+      <c r="L62" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M62">
+        <f ca="1"/>
+        <v>67</v>
+      </c>
+      <c r="N62" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O62">
+        <f ca="1"/>
+        <v>24455</v>
+      </c>
+      <c r="P62">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q62" t="str">
+        <f ca="1"/>
+        <v>Alderaan</v>
+      </c>
+      <c r="R62" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S62" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T62" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Revenge of the Sith </v>
+      </c>
+      <c r="U62" s="15">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="V62" s="4" cm="1">
+        <f t="array" aca="1" ref="V62" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W62" s="15">
+        <f ca="1"/>
+        <v>191</v>
+      </c>
+      <c r="X62" cm="1">
+        <f t="array" aca="1" ref="X62" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-16.641975308641975</v>
+      </c>
+      <c r="Y62" cm="1">
+        <f t="array" aca="1" ref="Y62" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>276.95534217344914</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25">
+      <c r="A63" t="str">
+        <f ca="1"/>
+        <v>San Hill</v>
+      </c>
+      <c r="B63">
+        <f ca="1"/>
+        <v>191</v>
+      </c>
+      <c r="C63">
+        <f ca="1"/>
+        <v>75</v>
+      </c>
+      <c r="D63">
+        <f ca="1"/>
+        <v>1.91</v>
+      </c>
+      <c r="E63" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F63" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G63">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I63">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J63" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K63" t="str">
+        <f ca="1"/>
+        <v>grey</v>
+      </c>
+      <c r="L63" t="str">
+        <f ca="1"/>
+        <v>gold</v>
+      </c>
+      <c r="M63" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N63" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O63" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P63">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q63" t="str">
+        <f ca="1"/>
+        <v>Muunilinst</v>
+      </c>
+      <c r="R63" t="str">
+        <f ca="1"/>
+        <v>Muun</v>
+      </c>
+      <c r="S63" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T63" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U63" s="15">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="V63" s="4" cm="1">
+        <f t="array" aca="1" ref="V63" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W63" s="15">
+        <f ca="1"/>
+        <v>191</v>
+      </c>
+      <c r="X63" cm="1">
+        <f t="array" aca="1" ref="X63" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-16.641975308641975</v>
+      </c>
+      <c r="Y63" cm="1">
+        <f t="array" aca="1" ref="Y63" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>276.95534217344914</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25">
+      <c r="A64" t="str">
+        <f ca="1"/>
+        <v>Qui-Gon Jinn</v>
+      </c>
+      <c r="B64">
+        <f ca="1"/>
+        <v>193</v>
+      </c>
+      <c r="C64">
+        <f ca="1"/>
+        <v>75.5</v>
+      </c>
+      <c r="D64">
+        <f ca="1"/>
+        <v>1.93</v>
+      </c>
+      <c r="E64">
+        <f ca="1"/>
+        <v>89</v>
+      </c>
+      <c r="F64">
+        <f ca="1"/>
+        <v>196</v>
+      </c>
+      <c r="G64">
+        <f ca="1"/>
+        <v>23.893258879433006</v>
+      </c>
+      <c r="H64">
+        <f ca="1"/>
+        <v>-9.4368068004023016</v>
+      </c>
+      <c r="I64">
+        <f ca="1"/>
+        <v>33</v>
+      </c>
+      <c r="J64" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K64" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L64" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M64">
+        <f ca="1"/>
+        <v>92</v>
+      </c>
+      <c r="N64" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O64">
+        <f ca="1"/>
+        <v>33580</v>
+      </c>
+      <c r="P64">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q64" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="R64" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S64" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T64" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U64" s="15">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="V64" s="4" cm="1">
+        <f t="array" aca="1" ref="V64" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W64" s="15">
+        <f ca="1"/>
+        <v>193</v>
+      </c>
+      <c r="X64" cm="1">
+        <f t="array" aca="1" ref="X64" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-18.641975308641975</v>
+      </c>
+      <c r="Y64" cm="1">
+        <f t="array" aca="1" ref="Y64" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>347.52324340801704</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25">
+      <c r="A65" t="str">
+        <f ca="1"/>
+        <v>Dooku</v>
+      </c>
+      <c r="B65">
+        <f ca="1"/>
+        <v>193</v>
+      </c>
+      <c r="C65">
+        <f ca="1"/>
+        <v>75.5</v>
+      </c>
+      <c r="D65">
+        <f ca="1"/>
+        <v>1.93</v>
+      </c>
+      <c r="E65">
+        <f ca="1"/>
+        <v>80</v>
+      </c>
+      <c r="F65">
+        <f ca="1"/>
+        <v>176.25</v>
+      </c>
+      <c r="G65">
+        <f ca="1"/>
+        <v>21.477086633198208</v>
+      </c>
+      <c r="H65">
+        <f ca="1"/>
+        <v>-11.852979046637099</v>
+      </c>
+      <c r="I65">
+        <f ca="1"/>
+        <v>45</v>
+      </c>
+      <c r="J65" t="str">
+        <f ca="1"/>
+        <v>white</v>
+      </c>
+      <c r="K65" t="str">
+        <f ca="1"/>
+        <v>fair</v>
+      </c>
+      <c r="L65" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="M65">
+        <f ca="1"/>
+        <v>102</v>
+      </c>
+      <c r="N65" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O65">
+        <f ca="1"/>
+        <v>37230</v>
+      </c>
+      <c r="P65">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q65" t="str">
+        <f ca="1"/>
+        <v>Serenno</v>
+      </c>
+      <c r="R65" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S65" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T65" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  Revenge of the Sith </v>
+      </c>
+      <c r="U65" s="15">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="V65" s="4" cm="1">
+        <f t="array" aca="1" ref="V65" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W65" s="15">
+        <f ca="1"/>
+        <v>193</v>
+      </c>
+      <c r="X65" cm="1">
+        <f t="array" aca="1" ref="X65" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-18.641975308641975</v>
+      </c>
+      <c r="Y65" cm="1">
+        <f t="array" aca="1" ref="Y65" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>347.52324340801704</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25">
+      <c r="A66" t="str">
+        <f ca="1"/>
+        <v>Wat Tambor</v>
+      </c>
+      <c r="B66">
+        <f ca="1"/>
+        <v>193</v>
+      </c>
+      <c r="C66">
+        <f ca="1"/>
+        <v>75.5</v>
+      </c>
+      <c r="D66">
+        <f ca="1"/>
+        <v>1.93</v>
+      </c>
+      <c r="E66">
+        <f ca="1"/>
+        <v>48</v>
+      </c>
+      <c r="F66">
+        <f ca="1"/>
+        <v>105.75</v>
+      </c>
+      <c r="G66">
+        <f ca="1"/>
+        <v>12.886251979918924</v>
+      </c>
+      <c r="H66">
+        <f ca="1"/>
+        <v>-20.443813699916383</v>
+      </c>
+      <c r="I66">
+        <f ca="1"/>
+        <v>59</v>
+      </c>
+      <c r="J66" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K66" t="str">
+        <f ca="1"/>
+        <v>green, grey</v>
+      </c>
+      <c r="L66" t="str">
+        <f ca="1"/>
+        <v>unknown</v>
+      </c>
+      <c r="M66" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N66" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O66" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P66">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q66" t="str">
+        <f ca="1"/>
+        <v>Skako</v>
+      </c>
+      <c r="R66" t="str">
+        <f ca="1"/>
+        <v>Skakoan</v>
+      </c>
+      <c r="S66" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T66" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U66" s="15">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="V66" s="4" cm="1">
+        <f t="array" aca="1" ref="V66" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W66" s="15">
+        <f ca="1"/>
+        <v>193</v>
+      </c>
+      <c r="X66" cm="1">
+        <f t="array" aca="1" ref="X66" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-18.641975308641975</v>
+      </c>
+      <c r="Y66" cm="1">
+        <f t="array" aca="1" ref="Y66" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>347.52324340801704</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25">
+      <c r="A67" t="str">
+        <f ca="1"/>
+        <v>Jar Jar Binks</v>
+      </c>
+      <c r="B67">
+        <f ca="1"/>
+        <v>196</v>
+      </c>
+      <c r="C67">
+        <f ca="1"/>
+        <v>77</v>
+      </c>
+      <c r="D67">
+        <f ca="1"/>
+        <v>1.96</v>
+      </c>
+      <c r="E67">
+        <f ca="1"/>
+        <v>66</v>
+      </c>
+      <c r="F67">
+        <f ca="1"/>
+        <v>145.5</v>
+      </c>
+      <c r="G67">
+        <f ca="1"/>
+        <v>17.180341524364849</v>
+      </c>
+      <c r="H67">
+        <f ca="1"/>
+        <v>-16.149724155470459</v>
+      </c>
+      <c r="I67">
+        <f ca="1"/>
+        <v>53</v>
+      </c>
+      <c r="J67" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K67" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="L67" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="M67">
+        <f ca="1"/>
+        <v>52</v>
+      </c>
+      <c r="N67" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O67">
+        <f ca="1"/>
+        <v>18980</v>
+      </c>
+      <c r="P67">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q67" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R67" t="str">
+        <f ca="1"/>
+        <v>Gungan</v>
+      </c>
+      <c r="S67" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T67" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace </v>
+      </c>
+      <c r="U67" s="15">
+        <f t="shared" ref="U67:U82" si="1">ROW()-1</f>
+        <v>66</v>
+      </c>
+      <c r="V67" s="4" cm="1">
+        <f t="array" aca="1" ref="V67" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W67" s="15">
+        <f ca="1"/>
+        <v>196</v>
+      </c>
+      <c r="X67" cm="1">
+        <f t="array" aca="1" ref="X67" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-21.641975308641975</v>
+      </c>
+      <c r="Y67" cm="1">
+        <f t="array" aca="1" ref="Y67" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>468.37509525986889</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25">
+      <c r="A68" t="str">
+        <f ca="1"/>
+        <v>Kit Fisto</v>
+      </c>
+      <c r="B68">
+        <f ca="1"/>
+        <v>196</v>
+      </c>
+      <c r="C68">
+        <f ca="1"/>
+        <v>77</v>
+      </c>
+      <c r="D68">
+        <f ca="1"/>
+        <v>1.96</v>
+      </c>
+      <c r="E68">
+        <f ca="1"/>
+        <v>87</v>
+      </c>
+      <c r="F68">
+        <f ca="1"/>
+        <v>191.75</v>
+      </c>
+      <c r="G68">
+        <f ca="1"/>
+        <v>22.646813827571847</v>
+      </c>
+      <c r="H68">
+        <f ca="1"/>
+        <v>-10.68325185226346</v>
+      </c>
+      <c r="I68">
+        <f ca="1"/>
+        <v>40</v>
+      </c>
+      <c r="J68" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K68" t="str">
+        <f ca="1"/>
+        <v>green</v>
+      </c>
+      <c r="L68" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="M68" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N68" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O68" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P68">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q68" t="str">
+        <f ca="1"/>
+        <v>Glee Anselm</v>
+      </c>
+      <c r="R68" t="str">
+        <f ca="1"/>
+        <v>Nautolan</v>
+      </c>
+      <c r="S68" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T68" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U68" s="15">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="V68" s="4" cm="1">
+        <f t="array" aca="1" ref="V68" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W68" s="15">
+        <f ca="1"/>
+        <v>196</v>
+      </c>
+      <c r="X68" cm="1">
+        <f t="array" aca="1" ref="X68" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-21.641975308641975</v>
+      </c>
+      <c r="Y68" cm="1">
+        <f t="array" aca="1" ref="Y68" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>468.37509525986889</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25">
+      <c r="A69" t="str">
+        <f ca="1"/>
+        <v>Mas Amedda</v>
+      </c>
+      <c r="B69">
+        <f ca="1"/>
+        <v>196</v>
+      </c>
+      <c r="C69">
+        <f ca="1"/>
+        <v>77</v>
+      </c>
+      <c r="D69">
+        <f ca="1"/>
+        <v>1.96</v>
+      </c>
+      <c r="E69" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F69" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G69">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I69">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J69" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K69" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="L69" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M69" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N69" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O69" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P69">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q69" t="str">
+        <f ca="1"/>
+        <v>Champala</v>
+      </c>
+      <c r="R69" t="str">
+        <f ca="1"/>
+        <v>Chagrian</v>
+      </c>
+      <c r="S69" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T69" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace </v>
+      </c>
+      <c r="U69" s="15">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="V69" s="4" cm="1">
+        <f t="array" aca="1" ref="V69" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>3</v>
+      </c>
+      <c r="W69" s="15">
+        <f ca="1"/>
+        <v>196</v>
+      </c>
+      <c r="X69" cm="1">
+        <f t="array" aca="1" ref="X69" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-21.641975308641975</v>
+      </c>
+      <c r="Y69" cm="1">
+        <f t="array" aca="1" ref="Y69" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>468.37509525986889</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25">
+      <c r="A70" t="str">
+        <f ca="1"/>
+        <v>Ki-Adi-Mundi</v>
+      </c>
+      <c r="B70">
+        <f ca="1"/>
+        <v>198</v>
+      </c>
+      <c r="C70">
+        <f ca="1"/>
+        <v>77.5</v>
+      </c>
+      <c r="D70">
+        <f ca="1"/>
+        <v>1.98</v>
+      </c>
+      <c r="E70">
+        <f ca="1"/>
+        <v>82</v>
+      </c>
+      <c r="F70">
+        <f ca="1"/>
+        <v>180.75</v>
+      </c>
+      <c r="G70">
+        <f ca="1"/>
+        <v>20.91623303744516</v>
+      </c>
+      <c r="H70">
+        <f ca="1"/>
+        <v>-12.413832642390147</v>
+      </c>
+      <c r="I70">
+        <f ca="1"/>
+        <v>46</v>
+      </c>
+      <c r="J70" t="str">
+        <f ca="1"/>
+        <v>white</v>
+      </c>
+      <c r="K70" t="str">
+        <f ca="1"/>
+        <v>pale</v>
+      </c>
+      <c r="L70" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M70">
+        <f ca="1"/>
+        <v>92</v>
+      </c>
+      <c r="N70" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O70">
+        <f ca="1"/>
+        <v>33580</v>
+      </c>
+      <c r="P70">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q70" t="str">
+        <f ca="1"/>
+        <v>Cerea</v>
+      </c>
+      <c r="R70" t="str">
+        <f ca="1"/>
+        <v>Cerean</v>
+      </c>
+      <c r="S70" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T70" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Attack of the Clones ,  The Phantom Menace ,  Revenge of the Sith </v>
+      </c>
+      <c r="U70" s="15">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="V70" s="4" cm="1">
+        <f t="array" aca="1" ref="V70" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W70" s="15">
+        <f ca="1"/>
+        <v>198</v>
+      </c>
+      <c r="X70" cm="1">
+        <f t="array" aca="1" ref="X70" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-23.641975308641975</v>
+      </c>
+      <c r="Y70" cm="1">
+        <f t="array" aca="1" ref="Y70" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>558.94299649443678</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25">
+      <c r="A71" t="str">
+        <f ca="1"/>
+        <v>Dexter Jettster</v>
+      </c>
+      <c r="B71">
+        <f ca="1"/>
+        <v>198</v>
+      </c>
+      <c r="C71">
+        <f ca="1"/>
+        <v>77.5</v>
+      </c>
+      <c r="D71">
+        <f ca="1"/>
+        <v>1.98</v>
+      </c>
+      <c r="E71">
+        <f ca="1"/>
+        <v>102</v>
+      </c>
+      <c r="F71">
+        <f ca="1"/>
+        <v>224.75</v>
+      </c>
+      <c r="G71">
+        <f ca="1"/>
+        <v>26.017753290480563</v>
+      </c>
+      <c r="H71">
+        <f ca="1"/>
+        <v>-7.3123123893547444</v>
+      </c>
+      <c r="I71">
+        <f ca="1"/>
+        <v>19</v>
+      </c>
+      <c r="J71" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K71" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="L71" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M71" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N71" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O71" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P71">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q71" t="str">
+        <f ca="1"/>
+        <v>Ojom</v>
+      </c>
+      <c r="R71" t="str">
+        <f ca="1"/>
+        <v>Besalisk</v>
+      </c>
+      <c r="S71" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T71" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U71" s="15">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="V71" s="4" cm="1">
+        <f t="array" aca="1" ref="V71" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W71" s="15">
+        <f ca="1"/>
+        <v>198</v>
+      </c>
+      <c r="X71" cm="1">
+        <f t="array" aca="1" ref="X71" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-23.641975308641975</v>
+      </c>
+      <c r="Y71" cm="1">
+        <f t="array" aca="1" ref="Y71" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>558.94299649443678</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25">
+      <c r="A72" t="str">
+        <f ca="1"/>
+        <v>IG-88</v>
+      </c>
+      <c r="B72">
+        <f ca="1"/>
+        <v>200</v>
+      </c>
+      <c r="C72">
+        <f ca="1"/>
+        <v>78.5</v>
+      </c>
+      <c r="D72">
+        <f ca="1"/>
+        <v>2</v>
+      </c>
+      <c r="E72">
+        <f ca="1"/>
+        <v>140</v>
+      </c>
+      <c r="F72">
+        <f ca="1"/>
+        <v>308.5</v>
+      </c>
+      <c r="G72">
+        <f ca="1"/>
+        <v>35</v>
+      </c>
+      <c r="H72">
+        <f ca="1"/>
+        <v>1.6699343201646926</v>
+      </c>
+      <c r="I72">
+        <f ca="1"/>
+        <v>5</v>
+      </c>
+      <c r="J72" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K72" t="str">
+        <f ca="1"/>
+        <v>metal</v>
+      </c>
+      <c r="L72" t="str">
+        <f ca="1"/>
+        <v>red</v>
+      </c>
+      <c r="M72">
+        <f ca="1"/>
+        <v>15</v>
+      </c>
+      <c r="N72" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O72">
+        <f ca="1"/>
+        <v>5475</v>
+      </c>
+      <c r="P72">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q72" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="R72" t="str">
+        <f ca="1"/>
+        <v>Droid</v>
+      </c>
+      <c r="S72" t="str">
+        <f ca="1"/>
+        <v>The Empire Strikes Back</v>
+      </c>
+      <c r="T72" t="str">
+        <f ca="1"/>
+        <v>The Empire Strikes Back</v>
+      </c>
+      <c r="U72" s="15">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="V72" s="4" cm="1">
+        <f t="array" aca="1" ref="V72" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W72" s="15">
+        <f ca="1"/>
+        <v>200</v>
+      </c>
+      <c r="X72" cm="1">
+        <f t="array" aca="1" ref="X72" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-25.641975308641975</v>
+      </c>
+      <c r="Y72" cm="1">
+        <f t="array" aca="1" ref="Y72" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>657.51089772900468</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25">
+      <c r="A73" t="str">
+        <f ca="1"/>
+        <v>Darth Vader</v>
+      </c>
+      <c r="B73">
+        <f ca="1"/>
+        <v>202</v>
+      </c>
+      <c r="C73">
+        <f ca="1"/>
+        <v>79.5</v>
+      </c>
+      <c r="D73">
+        <f ca="1"/>
+        <v>2.02</v>
+      </c>
+      <c r="E73">
+        <f ca="1"/>
+        <v>136</v>
+      </c>
+      <c r="F73">
+        <f ca="1"/>
+        <v>299.75</v>
+      </c>
+      <c r="G73">
+        <f ca="1"/>
+        <v>33.330065679835307</v>
+      </c>
+      <c r="H73">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <f ca="1"/>
+        <v>10</v>
+      </c>
+      <c r="J73" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K73" t="str">
+        <f ca="1"/>
+        <v>white</v>
+      </c>
+      <c r="L73" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M73">
+        <f ca="1"/>
+        <v>41.9</v>
+      </c>
+      <c r="N73" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O73">
+        <f ca="1"/>
+        <v>15293.5</v>
+      </c>
+      <c r="P73">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q73" t="str">
+        <f ca="1"/>
+        <v>Tatooine</v>
+      </c>
+      <c r="R73" t="str">
+        <f ca="1"/>
+        <v>Human</v>
+      </c>
+      <c r="S73" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T73" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Revenge of the Sith ,  Return of the Jedi ,  The Empire Strikes Back ,  A New Hope </v>
+      </c>
+      <c r="U73" s="15">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="V73" s="4" cm="1">
+        <f t="array" aca="1" ref="V73" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W73" s="15">
+        <f ca="1"/>
+        <v>202</v>
+      </c>
+      <c r="X73" cm="1">
+        <f t="array" aca="1" ref="X73" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-27.641975308641975</v>
+      </c>
+      <c r="Y73" cm="1">
+        <f t="array" aca="1" ref="Y73" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>764.07879896357258</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25">
+      <c r="A74" t="str">
+        <f ca="1"/>
+        <v>Rugor Nass</v>
+      </c>
+      <c r="B74">
+        <f ca="1"/>
+        <v>206</v>
+      </c>
+      <c r="C74">
+        <f ca="1"/>
+        <v>81</v>
+      </c>
+      <c r="D74">
+        <f ca="1"/>
+        <v>2.06</v>
+      </c>
+      <c r="E74" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F74" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G74">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I74">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J74" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K74" t="str">
+        <f ca="1"/>
+        <v>green</v>
+      </c>
+      <c r="L74" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="M74" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N74" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O74" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P74">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q74" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R74" t="str">
+        <f ca="1"/>
+        <v>Gungan</v>
+      </c>
+      <c r="S74" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T74" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U74" s="15">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="V74" s="4" cm="1">
+        <f t="array" aca="1" ref="V74" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W74" s="15">
+        <f ca="1"/>
+        <v>206</v>
+      </c>
+      <c r="X74" cm="1">
+        <f t="array" aca="1" ref="X74" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-31.641975308641975</v>
+      </c>
+      <c r="Y74" cm="1">
+        <f t="array" aca="1" ref="Y74" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>1001.2146014327084</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25">
+      <c r="A75" t="str">
+        <f ca="1"/>
+        <v>Tion Medon</v>
+      </c>
+      <c r="B75">
+        <f ca="1"/>
+        <v>206</v>
+      </c>
+      <c r="C75">
+        <f ca="1"/>
+        <v>81</v>
+      </c>
+      <c r="D75">
+        <f ca="1"/>
+        <v>2.06</v>
+      </c>
+      <c r="E75">
+        <f ca="1"/>
+        <v>80</v>
+      </c>
+      <c r="F75">
+        <f ca="1"/>
+        <v>176.25</v>
+      </c>
+      <c r="G75">
+        <f ca="1"/>
+        <v>18.851918182675089</v>
+      </c>
+      <c r="H75">
+        <f ca="1"/>
+        <v>-14.478147497160219</v>
+      </c>
+      <c r="I75">
+        <f ca="1"/>
+        <v>49</v>
+      </c>
+      <c r="J75" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K75" t="str">
+        <f ca="1"/>
+        <v>grey</v>
+      </c>
+      <c r="L75" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="M75" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N75" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O75" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P75">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q75" t="str">
+        <f ca="1"/>
+        <v>Utapau</v>
+      </c>
+      <c r="R75" t="str">
+        <f ca="1"/>
+        <v>Pau'an</v>
+      </c>
+      <c r="S75" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T75" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="U75" s="15">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="V75" s="4" cm="1">
+        <f t="array" aca="1" ref="V75" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>2</v>
+      </c>
+      <c r="W75" s="15">
+        <f ca="1"/>
+        <v>206</v>
+      </c>
+      <c r="X75" cm="1">
+        <f t="array" aca="1" ref="X75" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-31.641975308641975</v>
+      </c>
+      <c r="Y75" cm="1">
+        <f t="array" aca="1" ref="Y75" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>1001.2146014327084</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25">
+      <c r="A76" t="str">
+        <f ca="1"/>
+        <v>Taun We</v>
+      </c>
+      <c r="B76">
+        <f ca="1"/>
+        <v>213</v>
+      </c>
+      <c r="C76">
+        <f ca="1"/>
+        <v>83.5</v>
+      </c>
+      <c r="D76">
+        <f ca="1"/>
+        <v>2.13</v>
+      </c>
+      <c r="E76" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F76" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G76">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I76">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J76" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K76" t="str">
+        <f ca="1"/>
+        <v>grey</v>
+      </c>
+      <c r="L76" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="M76" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N76" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O76" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P76">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q76" t="str">
+        <f ca="1"/>
+        <v>Kamino</v>
+      </c>
+      <c r="R76" t="str">
+        <f ca="1"/>
+        <v>Kaminoan</v>
+      </c>
+      <c r="S76" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T76" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U76" s="15">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="V76" s="4" cm="1">
+        <f t="array" aca="1" ref="V76" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W76" s="15">
+        <f ca="1"/>
+        <v>213</v>
+      </c>
+      <c r="X76" cm="1">
+        <f t="array" aca="1" ref="X76" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-38.641975308641975</v>
+      </c>
+      <c r="Y76" cm="1">
+        <f t="array" aca="1" ref="Y76" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>1493.2022557536961</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25">
+      <c r="A77" t="str">
+        <f ca="1"/>
+        <v>Grievous</v>
+      </c>
+      <c r="B77">
+        <f ca="1"/>
+        <v>216</v>
+      </c>
+      <c r="C77">
+        <f ca="1"/>
+        <v>85</v>
+      </c>
+      <c r="D77">
+        <f ca="1"/>
+        <v>2.16</v>
+      </c>
+      <c r="E77">
+        <f ca="1"/>
+        <v>159</v>
+      </c>
+      <c r="F77">
+        <f ca="1"/>
+        <v>350.5</v>
+      </c>
+      <c r="G77">
+        <f ca="1"/>
+        <v>34.079218106995881</v>
+      </c>
+      <c r="H77">
+        <f ca="1"/>
+        <v>0.74915242716057406</v>
+      </c>
+      <c r="I77">
+        <f ca="1"/>
+        <v>7</v>
+      </c>
+      <c r="J77" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K77" t="str">
+        <f ca="1"/>
+        <v>brown, white</v>
+      </c>
+      <c r="L77" t="str">
+        <f ca="1"/>
+        <v>green, yellow</v>
+      </c>
+      <c r="M77" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N77" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O77" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P77">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q77" t="str">
+        <f ca="1"/>
+        <v>Kalee</v>
+      </c>
+      <c r="R77" t="str">
+        <f ca="1"/>
+        <v>Kaleesh</v>
+      </c>
+      <c r="S77" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T77" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="U77" s="15">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="V77" s="4" cm="1">
+        <f t="array" aca="1" ref="V77" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W77" s="15">
+        <f ca="1"/>
+        <v>216</v>
+      </c>
+      <c r="X77" cm="1">
+        <f t="array" aca="1" ref="X77" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-41.641975308641975</v>
+      </c>
+      <c r="Y77" cm="1">
+        <f t="array" aca="1" ref="Y77" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>1734.0541076055479</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25">
+      <c r="A78" t="str">
+        <f ca="1"/>
+        <v>Roos Tarpals</v>
+      </c>
+      <c r="B78">
+        <f ca="1"/>
+        <v>224</v>
+      </c>
+      <c r="C78">
+        <f ca="1"/>
+        <v>88</v>
+      </c>
+      <c r="D78">
+        <f ca="1"/>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E78">
+        <f ca="1"/>
+        <v>82</v>
+      </c>
+      <c r="F78">
+        <f ca="1"/>
+        <v>180.75</v>
+      </c>
+      <c r="G78">
+        <f ca="1"/>
+        <v>16.342474489795915</v>
+      </c>
+      <c r="H78">
+        <f ca="1"/>
+        <v>-16.987591190039392</v>
+      </c>
+      <c r="I78">
+        <f ca="1"/>
+        <v>56</v>
+      </c>
+      <c r="J78" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K78" t="str">
+        <f ca="1"/>
+        <v>grey</v>
+      </c>
+      <c r="L78" t="str">
+        <f ca="1"/>
+        <v>orange</v>
+      </c>
+      <c r="M78" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N78" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O78" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P78">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q78" t="str">
+        <f ca="1"/>
+        <v>Naboo</v>
+      </c>
+      <c r="R78" t="str">
+        <f ca="1"/>
+        <v>Gungan</v>
+      </c>
+      <c r="S78" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T78" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U78" s="15">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="V78" s="4" cm="1">
+        <f t="array" aca="1" ref="V78" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W78" s="15">
+        <f ca="1"/>
+        <v>224</v>
+      </c>
+      <c r="X78" cm="1">
+        <f t="array" aca="1" ref="X78" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-49.641975308641975</v>
+      </c>
+      <c r="Y78" cm="1">
+        <f t="array" aca="1" ref="Y78" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>2464.3257125438195</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25">
+      <c r="A79" t="str">
+        <f ca="1"/>
+        <v>Chewbacca</v>
+      </c>
+      <c r="B79">
+        <f ca="1"/>
+        <v>228</v>
+      </c>
+      <c r="C79">
+        <f ca="1"/>
+        <v>89.5</v>
+      </c>
+      <c r="D79">
+        <f ca="1"/>
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="E79">
+        <f ca="1"/>
+        <v>112</v>
+      </c>
+      <c r="F79">
+        <f ca="1"/>
+        <v>246.75</v>
+      </c>
+      <c r="G79">
+        <f ca="1"/>
+        <v>21.545090797168363</v>
+      </c>
+      <c r="H79">
+        <f ca="1"/>
+        <v>-11.784974882666944</v>
+      </c>
+      <c r="I79">
+        <f ca="1"/>
+        <v>44</v>
+      </c>
+      <c r="J79" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K79" t="str">
+        <f ca="1"/>
+        <v>unknown</v>
+      </c>
+      <c r="L79" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M79">
+        <f ca="1"/>
+        <v>200</v>
+      </c>
+      <c r="N79" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="O79">
+        <f ca="1"/>
+        <v>73000</v>
+      </c>
+      <c r="P79">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q79" t="str">
+        <f ca="1"/>
+        <v>Kashyyyk</v>
+      </c>
+      <c r="R79" t="str">
+        <f ca="1"/>
+        <v>Wookiee</v>
+      </c>
+      <c r="S79" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T79" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">Revenge of the Sith ,  Return of the Jedi ,  The Empire Strikes Back ,  A New Hope ,  The Force Awakens </v>
+      </c>
+      <c r="U79" s="15">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="V79" s="4" cm="1">
+        <f t="array" aca="1" ref="V79" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W79" s="15">
+        <f ca="1"/>
+        <v>228</v>
+      </c>
+      <c r="X79" cm="1">
+        <f t="array" aca="1" ref="X79" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-53.641975308641975</v>
+      </c>
+      <c r="Y79" cm="1">
+        <f t="array" aca="1" ref="Y79" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>2877.4615150129553</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25">
+      <c r="A80" t="str">
+        <f ca="1"/>
+        <v>Lama Su</v>
+      </c>
+      <c r="B80">
+        <f ca="1"/>
+        <v>229</v>
+      </c>
+      <c r="C80">
+        <f ca="1"/>
+        <v>90</v>
+      </c>
+      <c r="D80">
+        <f ca="1"/>
+        <v>2.29</v>
+      </c>
+      <c r="E80">
+        <f ca="1"/>
+        <v>88</v>
+      </c>
+      <c r="F80">
+        <f ca="1"/>
+        <v>194</v>
+      </c>
+      <c r="G80">
+        <f ca="1"/>
+        <v>16.780763143342039</v>
+      </c>
+      <c r="H80">
+        <f ca="1"/>
+        <v>-16.549302536493268</v>
+      </c>
+      <c r="I80">
+        <f ca="1"/>
+        <v>54</v>
+      </c>
+      <c r="J80" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K80" t="str">
+        <f ca="1"/>
+        <v>grey</v>
+      </c>
+      <c r="L80" t="str">
+        <f ca="1"/>
+        <v>black</v>
+      </c>
+      <c r="M80" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N80" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O80" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P80">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q80" t="str">
+        <f ca="1"/>
+        <v>Kamino</v>
+      </c>
+      <c r="R80" t="str">
+        <f ca="1"/>
+        <v>Kaminoan</v>
+      </c>
+      <c r="S80" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T80" t="str">
+        <f ca="1"/>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="U80" s="15">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="V80" s="4" cm="1">
+        <f t="array" aca="1" ref="V80" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W80" s="15">
+        <f ca="1"/>
+        <v>229</v>
+      </c>
+      <c r="X80" cm="1">
+        <f t="array" aca="1" ref="X80" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-54.641975308641975</v>
+      </c>
+      <c r="Y80" cm="1">
+        <f t="array" aca="1" ref="Y80" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>2985.7454656302393</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25">
+      <c r="A81" t="str">
+        <f ca="1"/>
+        <v>Tarfful</v>
+      </c>
+      <c r="B81">
+        <f ca="1"/>
+        <v>234</v>
+      </c>
+      <c r="C81">
+        <f ca="1"/>
+        <v>92</v>
+      </c>
+      <c r="D81">
+        <f ca="1"/>
+        <v>2.34</v>
+      </c>
+      <c r="E81">
+        <f ca="1"/>
+        <v>136</v>
+      </c>
+      <c r="F81">
+        <f ca="1"/>
+        <v>299.75</v>
+      </c>
+      <c r="G81">
+        <f ca="1"/>
+        <v>24.837460734896638</v>
+      </c>
+      <c r="H81">
+        <f ca="1"/>
+        <v>-8.4926049449386696</v>
+      </c>
+      <c r="I81">
+        <f ca="1"/>
+        <v>26</v>
+      </c>
+      <c r="J81" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="K81" t="str">
+        <f ca="1"/>
+        <v>brown</v>
+      </c>
+      <c r="L81" t="str">
+        <f ca="1"/>
+        <v>blue</v>
+      </c>
+      <c r="M81" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N81" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O81" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P81">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q81" t="str">
+        <f ca="1"/>
+        <v>Kashyyyk</v>
+      </c>
+      <c r="R81" t="str">
+        <f ca="1"/>
+        <v>Wookiee</v>
+      </c>
+      <c r="S81" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T81" t="str">
+        <f ca="1"/>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="U81" s="15">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="V81" s="4" cm="1">
+        <f t="array" aca="1" ref="V81" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W81" s="15">
+        <f ca="1"/>
+        <v>234</v>
+      </c>
+      <c r="X81" cm="1">
+        <f t="array" aca="1" ref="X81" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-59.641975308641975</v>
+      </c>
+      <c r="Y81" cm="1">
+        <f t="array" aca="1" ref="Y81" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>3557.1652187166592</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25">
+      <c r="A82" t="str">
+        <f ca="1"/>
+        <v>Yarael Poof</v>
+      </c>
+      <c r="B82">
+        <f ca="1"/>
+        <v>264</v>
+      </c>
+      <c r="C82">
+        <f ca="1"/>
+        <v>103.5</v>
+      </c>
+      <c r="D82">
+        <f ca="1"/>
+        <v>2.64</v>
+      </c>
+      <c r="E82" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="F82" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G82">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <f ca="1"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I82">
+        <f ca="1"/>
+        <v>60</v>
+      </c>
+      <c r="J82" t="str">
+        <f ca="1"/>
+        <v>none</v>
+      </c>
+      <c r="K82" t="str">
+        <f ca="1"/>
+        <v>white</v>
+      </c>
+      <c r="L82" t="str">
+        <f ca="1"/>
+        <v>yellow</v>
+      </c>
+      <c r="M82" t="str">
+        <f ca="1"/>
+        <v>NA</v>
+      </c>
+      <c r="N82" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="O82" t="e">
+        <f ca="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P82">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q82" t="str">
+        <f ca="1"/>
+        <v>Quermia</v>
+      </c>
+      <c r="R82" t="str">
+        <f ca="1"/>
+        <v>Quermian</v>
+      </c>
+      <c r="S82" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="T82" t="str">
+        <f ca="1"/>
+        <v>The Phantom Menace</v>
+      </c>
+      <c r="U82" s="15">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="V82" s="4" cm="1">
+        <f t="array" aca="1" ref="V82" ca="1">COUNT(_xlfn._xlws.FILTER(ordered_height,ordered_height=INDEX(ordered_height,ROW()-1)))</f>
+        <v>1</v>
+      </c>
+      <c r="W82" s="15">
+        <f ca="1"/>
+        <v>264</v>
+      </c>
+      <c r="X82" cm="1">
+        <f t="array" aca="1" ref="X82" ca="1">AVERAGE(ordered_height)-INDEX(ordered_height,ROW()-1)</f>
+        <v>-89.641975308641975</v>
+      </c>
+      <c r="Y82" cm="1">
+        <f t="array" aca="1" ref="Y82" ca="1">INDEX(diff_mean,ROW()-1)^2</f>
+        <v>8035.6837372351774</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
